--- a/research/traditional_assets/database/data/indonesia/indonesia_shoe.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_shoe.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.2125</v>
+        <v>-0.1392</v>
+      </c>
+      <c r="E2">
+        <v>-0.331</v>
       </c>
       <c r="G2">
-        <v>-0.4376757263355202</v>
+        <v>-0.1016495764600981</v>
       </c>
       <c r="H2">
-        <v>-0.4376757263355202</v>
+        <v>-0.1016495764600981</v>
       </c>
       <c r="I2">
-        <v>-0.2655420181193377</v>
+        <v>-0.05151582701738742</v>
       </c>
       <c r="J2">
-        <v>-0.2655420181193377</v>
+        <v>-0.05151582701738742</v>
       </c>
       <c r="K2">
-        <v>-10.25</v>
+        <v>-0.278</v>
       </c>
       <c r="L2">
-        <v>-0.3202124336144955</v>
+        <v>-0.006197057512260365</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.08</v>
+        <v>1.072</v>
       </c>
       <c r="V2">
-        <v>0.01952983725135624</v>
+        <v>0.02240334378265413</v>
       </c>
       <c r="W2">
-        <v>-0.485181834253684</v>
+        <v>-0.5295680068434558</v>
       </c>
       <c r="X2">
-        <v>0.09878717760595629</v>
+        <v>0.2014550926478818</v>
       </c>
       <c r="Y2">
-        <v>-0.5839690118596403</v>
+        <v>-0.7310230994913376</v>
       </c>
       <c r="Z2">
-        <v>0.6327837741667656</v>
+        <v>1.125777956233688</v>
       </c>
       <c r="AA2">
-        <v>-0.1999631699454474</v>
+        <v>-0.06010405773747279</v>
       </c>
       <c r="AB2">
-        <v>0.07964008736362582</v>
+        <v>0.1355629273275864</v>
       </c>
       <c r="AC2">
-        <v>-0.2796032573090731</v>
+        <v>-0.1956669850650592</v>
       </c>
       <c r="AD2">
-        <v>11.49</v>
+        <v>13.38</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.49</v>
+        <v>13.38</v>
       </c>
       <c r="AG2">
-        <v>10.41</v>
+        <v>12.308</v>
       </c>
       <c r="AH2">
-        <v>0.1720317412786345</v>
+        <v>0.2185203331700147</v>
       </c>
       <c r="AI2">
-        <v>0.2682323279484545</v>
+        <v>0.3343077730305075</v>
       </c>
       <c r="AJ2">
-        <v>0.1584233754375285</v>
+        <v>0.2045945676385518</v>
       </c>
       <c r="AK2">
-        <v>0.2493054890315164</v>
+        <v>0.3159867525865832</v>
       </c>
       <c r="AL2">
-        <v>0.8340000000000001</v>
+        <v>0.491</v>
       </c>
       <c r="AM2">
-        <v>0.8080000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="AN2">
-        <v>-1.770416024653312</v>
+        <v>-36.96132596685082</v>
       </c>
       <c r="AO2">
-        <v>-10.19184652278177</v>
+        <v>-4.706720977596741</v>
       </c>
       <c r="AP2">
-        <v>-1.604006163328197</v>
+        <v>-33.99999999999999</v>
       </c>
       <c r="AQ2">
-        <v>-10.51980198019802</v>
+        <v>-4.764948453608247</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.158</v>
+        <v>-0.08839999999999999</v>
+      </c>
+      <c r="E3">
+        <v>-0.331</v>
       </c>
       <c r="G3">
-        <v>-0.3877551020408164</v>
+        <v>-0.07506112469437652</v>
       </c>
       <c r="H3">
-        <v>-0.3877551020408164</v>
+        <v>-0.07506112469437652</v>
       </c>
       <c r="I3">
-        <v>-0.2078231292517007</v>
+        <v>-0.04400977995110025</v>
       </c>
       <c r="J3">
-        <v>-0.2078231292517007</v>
+        <v>-0.04400977995110025</v>
       </c>
       <c r="K3">
-        <v>-8.42</v>
+        <v>0.44</v>
       </c>
       <c r="L3">
-        <v>-0.2863945578231293</v>
+        <v>0.01075794621026895</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="V3">
-        <v>0.0234375</v>
+        <v>0.01778290993071594</v>
       </c>
       <c r="W3">
-        <v>-0.2110275689223058</v>
+        <v>0.01571428571428572</v>
       </c>
       <c r="X3">
-        <v>0.08546272248300103</v>
+        <v>0.138512068654592</v>
       </c>
       <c r="Y3">
-        <v>-0.2964902914053068</v>
+        <v>-0.1227977829403063</v>
       </c>
       <c r="Z3">
-        <v>0.7158509861212565</v>
+        <v>1.285435916776667</v>
       </c>
       <c r="AA3">
-        <v>-0.1487703920136353</v>
+        <v>-0.05657175183858194</v>
       </c>
       <c r="AB3">
-        <v>0.08091097103235381</v>
+        <v>0.130953909983137</v>
       </c>
       <c r="AC3">
-        <v>-0.2296813630459891</v>
+        <v>-0.1875256618217189</v>
       </c>
       <c r="AD3">
-        <v>4.06</v>
+        <v>5.35</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.06</v>
+        <v>5.35</v>
       </c>
       <c r="AG3">
-        <v>3.01</v>
+        <v>4.58</v>
       </c>
       <c r="AH3">
-        <v>0.08309455587392549</v>
+        <v>0.1099691675231244</v>
       </c>
       <c r="AI3">
-        <v>0.1161327231121281</v>
+        <v>0.1669266770670827</v>
       </c>
       <c r="AJ3">
-        <v>0.06295754026354319</v>
+        <v>0.09565580618212198</v>
       </c>
       <c r="AK3">
-        <v>0.08876437629017989</v>
+        <v>0.1464194373401534</v>
       </c>
       <c r="AL3">
-        <v>0.493</v>
+        <v>0.418</v>
       </c>
       <c r="AM3">
-        <v>0.468</v>
+        <v>0.413</v>
       </c>
       <c r="AN3">
-        <v>-0.978313253012048</v>
+        <v>51.94174757281554</v>
       </c>
       <c r="AO3">
-        <v>-12.39350912778905</v>
+        <v>-4.306220095693781</v>
       </c>
       <c r="AP3">
-        <v>-0.725301204819277</v>
+        <v>44.46601941747573</v>
       </c>
       <c r="AQ3">
-        <v>-13.05555555555556</v>
+        <v>-4.358353510895884</v>
       </c>
     </row>
     <row r="4">
@@ -844,25 +850,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.267</v>
+        <v>-0.19</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>-0.3762626262626262</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>-0.3762626262626262</v>
       </c>
       <c r="I4">
-        <v>-0.9157088122605365</v>
+        <v>-0.129040404040404</v>
       </c>
       <c r="J4">
-        <v>-0.9157088122605365</v>
+        <v>-0.129040404040404</v>
       </c>
       <c r="K4">
-        <v>-1.83</v>
+        <v>-0.718</v>
       </c>
       <c r="L4">
-        <v>-0.7011494252873564</v>
+        <v>-0.1813131313131313</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.03</v>
+        <v>0.302</v>
       </c>
       <c r="V4">
-        <v>0.002857142857142857</v>
+        <v>0.06637362637362637</v>
       </c>
       <c r="W4">
-        <v>-0.7593360995850622</v>
+        <v>-1.074850299401197</v>
       </c>
       <c r="X4">
-        <v>0.1121116327289115</v>
+        <v>0.2643981166411716</v>
       </c>
       <c r="Y4">
-        <v>-0.8714477323139738</v>
+        <v>-1.339248416042369</v>
       </c>
       <c r="Z4">
-        <v>0.2742749054224464</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="AA4">
-        <v>-0.2511559478772594</v>
+        <v>-0.06363636363636363</v>
       </c>
       <c r="AB4">
-        <v>0.07836920369489782</v>
+        <v>0.1401719446720359</v>
       </c>
       <c r="AC4">
-        <v>-0.3295251515721572</v>
+        <v>-0.2038083083083995</v>
       </c>
       <c r="AD4">
-        <v>7.43</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7.43</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AG4">
-        <v>7.399999999999999</v>
+        <v>7.728</v>
       </c>
       <c r="AH4">
-        <v>0.4143892916899052</v>
+        <v>0.638314785373609</v>
       </c>
       <c r="AI4">
-        <v>0.9433722701879127</v>
+        <v>1.00714912830804</v>
       </c>
       <c r="AJ4">
-        <v>0.4134078212290503</v>
+        <v>0.629418472063854</v>
       </c>
       <c r="AK4">
-        <v>0.9431557481519246</v>
+        <v>1.007430582714118</v>
       </c>
       <c r="AL4">
-        <v>0.341</v>
+        <v>0.073</v>
       </c>
       <c r="AM4">
-        <v>0.34</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AN4">
-        <v>-3.175213675213675</v>
+        <v>-17.26881720430107</v>
       </c>
       <c r="AO4">
-        <v>-7.008797653958944</v>
+        <v>-7.000000000000001</v>
       </c>
       <c r="AP4">
-        <v>-3.162393162393162</v>
+        <v>-16.61935483870968</v>
       </c>
       <c r="AQ4">
-        <v>-7.029411764705882</v>
+        <v>-7.097222222222223</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_shoe.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_shoe.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="idx_bima" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.1392</v>
-      </c>
-      <c r="E2">
-        <v>-0.331</v>
+        <v>-0.08630000000000002</v>
       </c>
       <c r="G2">
-        <v>-0.1016495764600981</v>
+        <v>-0.02222688194590061</v>
       </c>
       <c r="H2">
-        <v>-0.1016495764600981</v>
+        <v>-0.02222688194590061</v>
       </c>
       <c r="I2">
-        <v>-0.05151582701738742</v>
+        <v>-0.1057873768085553</v>
       </c>
       <c r="J2">
-        <v>-0.05151582701738742</v>
+        <v>-0.1057873768085553</v>
       </c>
       <c r="K2">
-        <v>-0.278</v>
+        <v>-10.771</v>
       </c>
       <c r="L2">
-        <v>-0.006197057512260365</v>
+        <v>-0.225854476829524</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.072</v>
+        <v>0.42</v>
       </c>
       <c r="V2">
-        <v>0.02240334378265413</v>
+        <v>0.02716688227684347</v>
       </c>
       <c r="W2">
-        <v>-0.5295680068434558</v>
+        <v>0.4224324857086536</v>
       </c>
       <c r="X2">
-        <v>0.2014550926478818</v>
+        <v>0.1749693777579125</v>
       </c>
       <c r="Y2">
-        <v>-0.7310230994913376</v>
+        <v>0.2474631079507411</v>
       </c>
       <c r="Z2">
-        <v>1.125777956233688</v>
+        <v>1.224358809786655</v>
       </c>
       <c r="AA2">
-        <v>-0.06010405773747279</v>
+        <v>-0.06514587607160327</v>
       </c>
       <c r="AB2">
-        <v>0.1355629273275864</v>
+        <v>0.1059351603960619</v>
       </c>
       <c r="AC2">
-        <v>-0.1956669850650592</v>
+        <v>-0.1710810364676651</v>
       </c>
       <c r="AD2">
-        <v>13.38</v>
+        <v>16.04</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.38</v>
+        <v>16.04</v>
       </c>
       <c r="AG2">
-        <v>12.308</v>
+        <v>15.62</v>
       </c>
       <c r="AH2">
-        <v>0.2185203331700147</v>
+        <v>0.5092063492063492</v>
       </c>
       <c r="AI2">
-        <v>0.3343077730305075</v>
+        <v>0.4359880402283229</v>
       </c>
       <c r="AJ2">
-        <v>0.2045945676385518</v>
+        <v>0.5025740025740025</v>
       </c>
       <c r="AK2">
-        <v>0.3159867525865832</v>
+        <v>0.429474841902667</v>
       </c>
       <c r="AL2">
-        <v>0.491</v>
+        <v>1.082</v>
       </c>
       <c r="AM2">
-        <v>0.485</v>
+        <v>1.073</v>
       </c>
       <c r="AN2">
-        <v>-36.96132596685082</v>
+        <v>-5.069532237673831</v>
       </c>
       <c r="AO2">
-        <v>-4.706720977596741</v>
+        <v>-4.662661737523106</v>
       </c>
       <c r="AP2">
-        <v>-33.99999999999999</v>
+        <v>-4.936788874841972</v>
       </c>
       <c r="AQ2">
-        <v>-4.764948453608247</v>
+        <v>-4.701770736253495</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Sepatu Bata Tbk. (IDX:BATA)</t>
+          <t>PT Primarindo Asia Infrastructure Tbk. (IDX:BIMA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,28 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08839999999999999</v>
-      </c>
-      <c r="E3">
-        <v>-0.331</v>
+        <v>-0.0888</v>
       </c>
       <c r="G3">
-        <v>-0.07506112469437652</v>
+        <v>0.1680129240710824</v>
       </c>
       <c r="H3">
-        <v>-0.07506112469437652</v>
+        <v>0.1680129240710824</v>
       </c>
       <c r="I3">
-        <v>-0.04400977995110025</v>
+        <v>0.05088852988691438</v>
       </c>
       <c r="J3">
-        <v>-0.04400977995110025</v>
+        <v>0.05088852988691438</v>
       </c>
       <c r="K3">
-        <v>0.44</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L3">
-        <v>0.01075794621026895</v>
+        <v>-0.01147011308562197</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +754,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.77</v>
+        <v>0.156</v>
       </c>
       <c r="V3">
-        <v>0.01778290993071594</v>
+        <v>0.04382022471910112</v>
       </c>
       <c r="W3">
-        <v>0.01571428571428572</v>
+        <v>1.245614035087719</v>
       </c>
       <c r="X3">
-        <v>0.138512068654592</v>
+        <v>0.2113353064073799</v>
       </c>
       <c r="Y3">
-        <v>-0.1227977829403063</v>
+        <v>1.034278728680339</v>
       </c>
       <c r="Z3">
-        <v>1.285435916776667</v>
+        <v>0.8069352105331771</v>
       </c>
       <c r="AA3">
-        <v>-0.05657175183858194</v>
+        <v>0.04106374657802112</v>
       </c>
       <c r="AB3">
-        <v>0.130953909983137</v>
+        <v>0.1066029927542832</v>
       </c>
       <c r="AC3">
-        <v>-0.1875256618217189</v>
+        <v>-0.06553924617626206</v>
       </c>
       <c r="AD3">
-        <v>5.35</v>
+        <v>7.66</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.35</v>
+        <v>7.66</v>
       </c>
       <c r="AG3">
-        <v>4.58</v>
+        <v>7.504</v>
       </c>
       <c r="AH3">
-        <v>0.1099691675231244</v>
+        <v>0.6827094474153298</v>
       </c>
       <c r="AI3">
-        <v>0.1669266770670827</v>
+        <v>0.5842868039664378</v>
       </c>
       <c r="AJ3">
-        <v>0.09565580618212198</v>
+        <v>0.67823571945047</v>
       </c>
       <c r="AK3">
-        <v>0.1464194373401534</v>
+        <v>0.5792805311100818</v>
       </c>
       <c r="AL3">
-        <v>0.418</v>
+        <v>0.242</v>
       </c>
       <c r="AM3">
-        <v>0.413</v>
+        <v>0.24</v>
       </c>
       <c r="AN3">
-        <v>51.94174757281554</v>
+        <v>22.13872832369943</v>
       </c>
       <c r="AO3">
-        <v>-4.306220095693781</v>
+        <v>1.301652892561983</v>
       </c>
       <c r="AP3">
-        <v>44.46601941747573</v>
+        <v>21.6878612716763</v>
       </c>
       <c r="AQ3">
-        <v>-4.358353510895884</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +837,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Primarindo Asia Infrastructure Tbk. (IDX:BIMA)</t>
+          <t>PT Sepatu Bata Tbk. (IDX:BATA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,25 +846,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.19</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="G4">
-        <v>-0.3762626262626262</v>
+        <v>-0.05060240963855422</v>
       </c>
       <c r="H4">
-        <v>-0.3762626262626262</v>
+        <v>-0.05060240963855422</v>
       </c>
       <c r="I4">
-        <v>-0.129040404040404</v>
+        <v>-0.1291566265060241</v>
       </c>
       <c r="J4">
-        <v>-0.129040404040404</v>
+        <v>-0.1291566265060241</v>
       </c>
       <c r="K4">
-        <v>-0.718</v>
+        <v>-10.7</v>
       </c>
       <c r="L4">
-        <v>-0.1813131313131313</v>
+        <v>-0.2578313253012048</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +888,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.302</v>
+        <v>0.264</v>
       </c>
       <c r="V4">
-        <v>0.06637362637362637</v>
+        <v>0.02218487394957983</v>
       </c>
       <c r="W4">
-        <v>-1.074850299401197</v>
+        <v>-0.400749063670412</v>
       </c>
       <c r="X4">
-        <v>0.2643981166411716</v>
+        <v>0.1386034491084451</v>
       </c>
       <c r="Y4">
-        <v>-1.339248416042369</v>
+        <v>-0.5393525127788571</v>
       </c>
       <c r="Z4">
-        <v>0.4931506849315068</v>
+        <v>1.326726342710998</v>
       </c>
       <c r="AA4">
-        <v>-0.06363636363636363</v>
+        <v>-0.1713554987212277</v>
       </c>
       <c r="AB4">
-        <v>0.1401719446720359</v>
+        <v>0.1052673280378406</v>
       </c>
       <c r="AC4">
-        <v>-0.2038083083083995</v>
+        <v>-0.2766228267590682</v>
       </c>
       <c r="AD4">
-        <v>8.029999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8.029999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AG4">
-        <v>7.728</v>
+        <v>8.116000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.638314785373609</v>
+        <v>0.4132149901380671</v>
       </c>
       <c r="AI4">
-        <v>1.00714912830804</v>
+        <v>0.3538851351351352</v>
       </c>
       <c r="AJ4">
-        <v>0.629418472063854</v>
+        <v>0.4054756195043965</v>
       </c>
       <c r="AK4">
-        <v>1.007430582714118</v>
+        <v>0.3466006149641271</v>
       </c>
       <c r="AL4">
-        <v>0.073</v>
+        <v>0.84</v>
       </c>
       <c r="AM4">
-        <v>0.07199999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="AN4">
-        <v>-17.26881720430107</v>
+        <v>-2.387464387464388</v>
       </c>
       <c r="AO4">
-        <v>-7.000000000000001</v>
+        <v>-6.380952380952381</v>
       </c>
       <c r="AP4">
-        <v>-16.61935483870968</v>
+        <v>-2.312250712250713</v>
       </c>
       <c r="AQ4">
-        <v>-7.097222222222223</v>
+        <v>-6.434573829531813</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PT Primarindo Asia Infrastructure Tbk. (IDX:BIMA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IDX:BIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shoe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.30165289256198</v>
+      </c>
+      <c r="F2">
+        <v>4.54985431294226</v>
+      </c>
+      <c r="G2">
+        <v>22.1387283236994</v>
+      </c>
+      <c r="H2">
+        <v>6.80982658959538</v>
+      </c>
+      <c r="I2">
+        <v>0.68270944741533</v>
+      </c>
+      <c r="J2">
+        <v>0.21</v>
+      </c>
+      <c r="K2">
+        <v>3.56</v>
+      </c>
+      <c r="L2">
+        <v>9.97147979227814</v>
+      </c>
+      <c r="M2">
+        <v>11.064</v>
+      </c>
+      <c r="N2">
+        <v>12.1716797922781</v>
+      </c>
+      <c r="O2">
+        <v>7.66</v>
+      </c>
+      <c r="P2">
+        <v>2.3562</v>
+      </c>
+      <c r="Q2">
+        <v>0.106602992754283</v>
+      </c>
+      <c r="R2">
+        <v>0.100432603275458</v>
+      </c>
+      <c r="S2">
+        <v>0.0579284448946194</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.21133530640738</v>
+      </c>
+      <c r="X2">
+        <v>0.116576181361339</v>
+      </c>
+      <c r="Y2">
+        <v>2.33640330888167</v>
+      </c>
+      <c r="Z2">
+        <v>1.05321357853422</v>
+      </c>
+      <c r="AA2">
+        <v>7.660000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.07426723704438384</v>
+      </c>
+      <c r="AC2">
+        <v>1.301652892561983</v>
+      </c>
+      <c r="AD2">
+        <v>7.660000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0.242</v>
+      </c>
+      <c r="AF2">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="AG2">
+        <v>0.346</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>3.56</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.05199999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>0.242</v>
+      </c>
+      <c r="AS2">
+        <v>7.66</v>
+      </c>
+      <c r="AT2">
+        <v>0.156</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1032193575964124</v>
+      </c>
+      <c r="C2">
+        <v>11.80113804271727</v>
+      </c>
+      <c r="D2">
+        <v>11.64513804271727</v>
+      </c>
+      <c r="E2">
+        <v>-7.660000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.156</v>
+      </c>
+      <c r="H2">
+        <v>3.56</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K2">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L2">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="O2">
+        <v>0.1200466666666667</v>
+      </c>
+      <c r="P2">
+        <v>0.4256200000000001</v>
+      </c>
+      <c r="Q2">
+        <v>0.45662</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1032193575964124</v>
+      </c>
+      <c r="T2">
+        <v>0.8723408754896527</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1030382950097002</v>
+      </c>
+      <c r="C3">
+        <v>11.72176112459258</v>
+      </c>
+      <c r="D3">
+        <v>11.67796112459258</v>
+      </c>
+      <c r="E3">
+        <v>-7.547800000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.1122</v>
+      </c>
+      <c r="G3">
+        <v>0.156</v>
+      </c>
+      <c r="H3">
+        <v>3.56</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K3">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L3">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.005015340000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.5406513266666667</v>
+      </c>
+      <c r="O3">
+        <v>0.1189432918666667</v>
+      </c>
+      <c r="P3">
+        <v>0.4217080348</v>
+      </c>
+      <c r="Q3">
+        <v>0.4527080348</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1037269040502023</v>
+      </c>
+      <c r="T3">
+        <v>0.8792138642056317</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>108.7995363557937</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1028572324229881</v>
+      </c>
+      <c r="C4">
+        <v>11.64256976028855</v>
+      </c>
+      <c r="D4">
+        <v>11.71096976028855</v>
+      </c>
+      <c r="E4">
+        <v>-7.435600000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.2244</v>
+      </c>
+      <c r="G4">
+        <v>0.156</v>
+      </c>
+      <c r="H4">
+        <v>3.56</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K4">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L4">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.01003068</v>
+      </c>
+      <c r="N4">
+        <v>0.5356359866666668</v>
+      </c>
+      <c r="O4">
+        <v>0.1178399170666667</v>
+      </c>
+      <c r="P4">
+        <v>0.4177960696000001</v>
+      </c>
+      <c r="Q4">
+        <v>0.4487960696000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1042448085948859</v>
+      </c>
+      <c r="T4">
+        <v>0.8862271179974471</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>54.39976817789688</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.102676169836276</v>
+      </c>
+      <c r="C5">
+        <v>11.56356552771073</v>
+      </c>
+      <c r="D5">
+        <v>11.74416552771073</v>
+      </c>
+      <c r="E5">
+        <v>-7.323400000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.3366</v>
+      </c>
+      <c r="G5">
+        <v>0.156</v>
+      </c>
+      <c r="H5">
+        <v>3.56</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K5">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L5">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.01504602</v>
+      </c>
+      <c r="N5">
+        <v>0.5306206466666668</v>
+      </c>
+      <c r="O5">
+        <v>0.1167365422666667</v>
+      </c>
+      <c r="P5">
+        <v>0.4138841044000001</v>
+      </c>
+      <c r="Q5">
+        <v>0.4448841044</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1047733915837897</v>
+      </c>
+      <c r="T5">
+        <v>0.8933849749602278</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>36.26651211859792</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1024951072495639</v>
+      </c>
+      <c r="C6">
+        <v>11.48475002270641</v>
+      </c>
+      <c r="D6">
+        <v>11.77755002270641</v>
+      </c>
+      <c r="E6">
+        <v>-7.211200000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.4488</v>
+      </c>
+      <c r="G6">
+        <v>0.156</v>
+      </c>
+      <c r="H6">
+        <v>3.56</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K6">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L6">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M6">
+        <v>0.02006136</v>
+      </c>
+      <c r="N6">
+        <v>0.5256053066666667</v>
+      </c>
+      <c r="O6">
+        <v>0.1156331674666667</v>
+      </c>
+      <c r="P6">
+        <v>0.4099721392</v>
+      </c>
+      <c r="Q6">
+        <v>0.4409721392</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1053129867182958</v>
+      </c>
+      <c r="T6">
+        <v>0.9006919539430663</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>27.19988408894844</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1023140446628518</v>
+      </c>
+      <c r="C7">
+        <v>11.4061248593203</v>
+      </c>
+      <c r="D7">
+        <v>11.8111248593203</v>
+      </c>
+      <c r="E7">
+        <v>-7.099000000000001</v>
+      </c>
+      <c r="F7">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.156</v>
+      </c>
+      <c r="H7">
+        <v>3.56</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K7">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L7">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M7">
+        <v>0.0250767</v>
+      </c>
+      <c r="N7">
+        <v>0.5205899666666668</v>
+      </c>
+      <c r="O7">
+        <v>0.1145297926666667</v>
+      </c>
+      <c r="P7">
+        <v>0.4060601740000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.4370601740000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1058639417503703</v>
+      </c>
+      <c r="T7">
+        <v>0.9081527640623859</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>21.75990727115875</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1021329820761397</v>
+      </c>
+      <c r="C8">
+        <v>11.32769167005467</v>
+      </c>
+      <c r="D8">
+        <v>11.84489167005467</v>
+      </c>
+      <c r="E8">
+        <v>-6.986800000000001</v>
+      </c>
+      <c r="F8">
+        <v>0.6732</v>
+      </c>
+      <c r="G8">
+        <v>0.156</v>
+      </c>
+      <c r="H8">
+        <v>3.56</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K8">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L8">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M8">
+        <v>0.03009204</v>
+      </c>
+      <c r="N8">
+        <v>0.5155746266666668</v>
+      </c>
+      <c r="O8">
+        <v>0.1134264178666667</v>
+      </c>
+      <c r="P8">
+        <v>0.4021482088000001</v>
+      </c>
+      <c r="Q8">
+        <v>0.4331482088</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1064266192299359</v>
+      </c>
+      <c r="T8">
+        <v>0.9157723148225417</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>18.13325605929896</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1019519194894276</v>
+      </c>
+      <c r="C9">
+        <v>11.24945210613395</v>
+      </c>
+      <c r="D9">
+        <v>11.87885210613395</v>
+      </c>
+      <c r="E9">
+        <v>-6.874600000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.7854000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.156</v>
+      </c>
+      <c r="H9">
+        <v>3.56</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K9">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L9">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M9">
+        <v>0.03510738000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.5105592866666667</v>
+      </c>
+      <c r="O9">
+        <v>0.1123230430666667</v>
+      </c>
+      <c r="P9">
+        <v>0.3982362436</v>
+      </c>
+      <c r="Q9">
+        <v>0.4292362436</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1070013973004598</v>
+      </c>
+      <c r="T9">
+        <v>0.9235557268893678</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.034866</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.54279090797054</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1017708569027155</v>
+      </c>
+      <c r="C10">
+        <v>11.17140783777391</v>
+      </c>
+      <c r="D10">
+        <v>11.91300783777391</v>
+      </c>
+      <c r="E10">
+        <v>-6.762400000000001</v>
+      </c>
+      <c r="F10">
+        <v>0.8976000000000001</v>
+      </c>
+      <c r="G10">
+        <v>0.156</v>
+      </c>
+      <c r="H10">
+        <v>3.56</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K10">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L10">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M10">
+        <v>0.04012272000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.5055439466666667</v>
+      </c>
+      <c r="O10">
+        <v>0.1112196682666667</v>
+      </c>
+      <c r="P10">
+        <v>0.3943242784</v>
+      </c>
+      <c r="Q10">
+        <v>0.4253242784</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1075886705464299</v>
+      </c>
+      <c r="T10">
+        <v>0.9315083435663422</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.034866</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.59994204447422</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1016670143160034</v>
+      </c>
+      <c r="C11">
+        <v>11.07888552666777</v>
+      </c>
+      <c r="D11">
+        <v>11.93268552666777</v>
+      </c>
+      <c r="E11">
+        <v>-6.650200000000001</v>
+      </c>
+      <c r="F11">
+        <v>1.0098</v>
+      </c>
+      <c r="G11">
+        <v>0.156</v>
+      </c>
+      <c r="H11">
+        <v>3.56</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K11">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L11">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M11">
+        <v>0.04624884</v>
+      </c>
+      <c r="N11">
+        <v>0.4994178266666667</v>
+      </c>
+      <c r="O11">
+        <v>0.1098719218666667</v>
+      </c>
+      <c r="P11">
+        <v>0.3895459048000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.4205459048</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.108188850896707</v>
+      </c>
+      <c r="T11">
+        <v>0.9396357430274259</v>
+      </c>
+      <c r="U11">
+        <v>0.0458</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.035724</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.79849411718579</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1014945317292913</v>
+      </c>
+      <c r="C12">
+        <v>10.99951423451981</v>
+      </c>
+      <c r="D12">
+        <v>11.96551423451981</v>
+      </c>
+      <c r="E12">
+        <v>-6.538000000000001</v>
+      </c>
+      <c r="F12">
+        <v>1.122</v>
+      </c>
+      <c r="G12">
+        <v>0.156</v>
+      </c>
+      <c r="H12">
+        <v>3.56</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K12">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L12">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M12">
+        <v>0.05138760000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.4942790666666668</v>
+      </c>
+      <c r="O12">
+        <v>0.1087413946666667</v>
+      </c>
+      <c r="P12">
+        <v>0.3855376720000001</v>
+      </c>
+      <c r="Q12">
+        <v>0.4165376720000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1088023685881014</v>
+      </c>
+      <c r="T12">
+        <v>0.9479437513654225</v>
+      </c>
+      <c r="U12">
+        <v>0.0458</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.035724</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.61864470546721</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1015108091425792</v>
+      </c>
+      <c r="C13">
+        <v>10.88420842831096</v>
+      </c>
+      <c r="D13">
+        <v>11.96240842831096</v>
+      </c>
+      <c r="E13">
+        <v>-6.425800000000001</v>
+      </c>
+      <c r="F13">
+        <v>1.2342</v>
+      </c>
+      <c r="G13">
+        <v>0.156</v>
+      </c>
+      <c r="H13">
+        <v>3.56</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K13">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L13">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M13">
+        <v>0.05924160000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.4864250666666667</v>
+      </c>
+      <c r="O13">
+        <v>0.1070135146666667</v>
+      </c>
+      <c r="P13">
+        <v>0.379411552</v>
+      </c>
+      <c r="Q13">
+        <v>0.410411552</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1094296731939092</v>
+      </c>
+      <c r="T13">
+        <v>0.9564384565200036</v>
+      </c>
+      <c r="U13">
+        <v>0.048</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.03744</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>9.210869839212085</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1013554865558671</v>
+      </c>
+      <c r="C14">
+        <v>10.80171057472033</v>
+      </c>
+      <c r="D14">
+        <v>11.99211057472033</v>
+      </c>
+      <c r="E14">
+        <v>-6.313600000000001</v>
+      </c>
+      <c r="F14">
+        <v>1.3464</v>
+      </c>
+      <c r="G14">
+        <v>0.156</v>
+      </c>
+      <c r="H14">
+        <v>3.56</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K14">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L14">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M14">
+        <v>0.06462720000000001</v>
+      </c>
+      <c r="N14">
+        <v>0.4810394666666667</v>
+      </c>
+      <c r="O14">
+        <v>0.1058286826666667</v>
+      </c>
+      <c r="P14">
+        <v>0.3752107840000001</v>
+      </c>
+      <c r="Q14">
+        <v>0.406210784</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1100712347225762</v>
+      </c>
+      <c r="T14">
+        <v>0.9651262231553703</v>
+      </c>
+      <c r="U14">
+        <v>0.048</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.03744</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.443297352611079</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.101200163969155</v>
+      </c>
+      <c r="C15">
+        <v>10.71936058658126</v>
+      </c>
+      <c r="D15">
+        <v>12.02196058658126</v>
+      </c>
+      <c r="E15">
+        <v>-6.201400000000001</v>
+      </c>
+      <c r="F15">
+        <v>1.4586</v>
+      </c>
+      <c r="G15">
+        <v>0.156</v>
+      </c>
+      <c r="H15">
+        <v>3.56</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K15">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L15">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M15">
+        <v>0.07001280000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.4756538666666668</v>
+      </c>
+      <c r="O15">
+        <v>0.1046438506666667</v>
+      </c>
+      <c r="P15">
+        <v>0.3710100160000001</v>
+      </c>
+      <c r="Q15">
+        <v>0.402010016</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1107275447921321</v>
+      </c>
+      <c r="T15">
+        <v>0.9740137085639639</v>
+      </c>
+      <c r="U15">
+        <v>0.048</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.03744</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.793812940871764</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1012086413824429</v>
+      </c>
+      <c r="C16">
+        <v>10.60552755746597</v>
+      </c>
+      <c r="D16">
+        <v>12.02032755746597</v>
+      </c>
+      <c r="E16">
+        <v>-6.089200000000001</v>
+      </c>
+      <c r="F16">
+        <v>1.5708</v>
+      </c>
+      <c r="G16">
+        <v>0.156</v>
+      </c>
+      <c r="H16">
+        <v>3.56</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K16">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L16">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M16">
+        <v>0.07775460000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.4679120666666667</v>
+      </c>
+      <c r="O16">
+        <v>0.1029406546666667</v>
+      </c>
+      <c r="P16">
+        <v>0.3649714120000001</v>
+      </c>
+      <c r="Q16">
+        <v>0.395971412</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1113991178865615</v>
+      </c>
+      <c r="T16">
+        <v>0.9831078796797341</v>
+      </c>
+      <c r="U16">
+        <v>0.0495</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.017805591780637</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1010650187957308</v>
+      </c>
+      <c r="C17">
+        <v>10.52105404932801</v>
+      </c>
+      <c r="D17">
+        <v>12.04805404932801</v>
+      </c>
+      <c r="E17">
+        <v>-5.977000000000001</v>
+      </c>
+      <c r="F17">
+        <v>1.683</v>
+      </c>
+      <c r="G17">
+        <v>0.156</v>
+      </c>
+      <c r="H17">
+        <v>3.56</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K17">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L17">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M17">
+        <v>0.08330850000000001</v>
+      </c>
+      <c r="N17">
+        <v>0.4623581666666667</v>
+      </c>
+      <c r="O17">
+        <v>0.1017187966666667</v>
+      </c>
+      <c r="P17">
+        <v>0.3606393700000001</v>
+      </c>
+      <c r="Q17">
+        <v>0.39163937</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1120864927008597</v>
+      </c>
+      <c r="T17">
+        <v>0.9924160312923461</v>
+      </c>
+      <c r="U17">
+        <v>0.0495</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.549951885661928</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1010961162090186</v>
+      </c>
+      <c r="C18">
+        <v>10.40283981699884</v>
+      </c>
+      <c r="D18">
+        <v>12.04203981699884</v>
+      </c>
+      <c r="E18">
+        <v>-5.864800000000001</v>
+      </c>
+      <c r="F18">
+        <v>1.7952</v>
+      </c>
+      <c r="G18">
+        <v>0.156</v>
+      </c>
+      <c r="H18">
+        <v>3.56</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K18">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L18">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M18">
+        <v>0.09137568000000001</v>
+      </c>
+      <c r="N18">
+        <v>0.4542909866666667</v>
+      </c>
+      <c r="O18">
+        <v>0.09994401706666668</v>
+      </c>
+      <c r="P18">
+        <v>0.3543469696000001</v>
+      </c>
+      <c r="Q18">
+        <v>0.3853469696</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1127902335821651</v>
+      </c>
+      <c r="T18">
+        <v>1.001945805562401</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.039702</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.971683785736715</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1009634136223065</v>
+      </c>
+      <c r="C19">
+        <v>10.31634641417374</v>
+      </c>
+      <c r="D19">
+        <v>12.06774641417374</v>
+      </c>
+      <c r="E19">
+        <v>-5.752600000000001</v>
+      </c>
+      <c r="F19">
+        <v>1.9074</v>
+      </c>
+      <c r="G19">
+        <v>0.156</v>
+      </c>
+      <c r="H19">
+        <v>3.56</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K19">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L19">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M19">
+        <v>0.09708666000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.4485800066666668</v>
+      </c>
+      <c r="O19">
+        <v>0.09868760146666669</v>
+      </c>
+      <c r="P19">
+        <v>0.3498924052000001</v>
+      </c>
+      <c r="Q19">
+        <v>0.3808924052000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1135109320750681</v>
+      </c>
+      <c r="T19">
+        <v>1.011705212947397</v>
+      </c>
+      <c r="U19">
+        <v>0.0509</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.039702</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.620408268928674</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1008307110355944</v>
+      </c>
+      <c r="C20">
+        <v>10.22996299983287</v>
+      </c>
+      <c r="D20">
+        <v>12.09356299983287</v>
+      </c>
+      <c r="E20">
+        <v>-5.640400000000001</v>
+      </c>
+      <c r="F20">
+        <v>2.0196</v>
+      </c>
+      <c r="G20">
+        <v>0.156</v>
+      </c>
+      <c r="H20">
+        <v>3.56</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K20">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L20">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M20">
+        <v>0.10279764</v>
+      </c>
+      <c r="N20">
+        <v>0.4428690266666667</v>
+      </c>
+      <c r="O20">
+        <v>0.09743118586666667</v>
+      </c>
+      <c r="P20">
+        <v>0.3454378408000001</v>
+      </c>
+      <c r="Q20">
+        <v>0.3764378408</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1142492085799932</v>
+      </c>
+      <c r="T20">
+        <v>1.021702654658857</v>
+      </c>
+      <c r="U20">
+        <v>0.0509</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.039702</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.308163365099302</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1006980084488823</v>
+      </c>
+      <c r="C21">
+        <v>10.14369028138618</v>
+      </c>
+      <c r="D21">
+        <v>12.11949028138618</v>
+      </c>
+      <c r="E21">
+        <v>-5.528200000000001</v>
+      </c>
+      <c r="F21">
+        <v>2.1318</v>
+      </c>
+      <c r="G21">
+        <v>0.156</v>
+      </c>
+      <c r="H21">
+        <v>3.56</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K21">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L21">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M21">
+        <v>0.10850862</v>
+      </c>
+      <c r="N21">
+        <v>0.4371580466666667</v>
+      </c>
+      <c r="O21">
+        <v>0.09617477026666668</v>
+      </c>
+      <c r="P21">
+        <v>0.3409832764</v>
+      </c>
+      <c r="Q21">
+        <v>0.3719832764</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1150057141344226</v>
+      </c>
+      <c r="T21">
+        <v>1.031946946782945</v>
+      </c>
+      <c r="U21">
+        <v>0.0509</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.039702</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.02878634588355</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1005653058621702</v>
+      </c>
+      <c r="C22">
+        <v>10.05752897232315</v>
+      </c>
+      <c r="D22">
+        <v>12.14552897232315</v>
+      </c>
+      <c r="E22">
+        <v>-5.416</v>
+      </c>
+      <c r="F22">
+        <v>2.244</v>
+      </c>
+      <c r="G22">
+        <v>0.156</v>
+      </c>
+      <c r="H22">
+        <v>3.56</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K22">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L22">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M22">
+        <v>0.1142196</v>
+      </c>
+      <c r="N22">
+        <v>0.4314470666666667</v>
+      </c>
+      <c r="O22">
+        <v>0.09491835466666668</v>
+      </c>
+      <c r="P22">
+        <v>0.336528712</v>
+      </c>
+      <c r="Q22">
+        <v>0.367528712</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1157811323277128</v>
+      </c>
+      <c r="T22">
+        <v>1.042447346210135</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.039702</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.777347028589372</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1004326032754581</v>
+      </c>
+      <c r="C23">
+        <v>9.971479792278144</v>
+      </c>
+      <c r="D23">
+        <v>12.17167979227814</v>
+      </c>
+      <c r="E23">
+        <v>-5.303800000000001</v>
+      </c>
+      <c r="F23">
+        <v>2.3562</v>
+      </c>
+      <c r="G23">
+        <v>0.156</v>
+      </c>
+      <c r="H23">
+        <v>3.56</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K23">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L23">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M23">
+        <v>0.11993058</v>
+      </c>
+      <c r="N23">
+        <v>0.4257360866666667</v>
+      </c>
+      <c r="O23">
+        <v>0.09366193906666669</v>
+      </c>
+      <c r="P23">
+        <v>0.3320741476</v>
+      </c>
+      <c r="Q23">
+        <v>0.3630741476</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1165761813613394</v>
+      </c>
+      <c r="T23">
+        <v>1.053213578534216</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.039702</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.54985431294226</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.100746060688746</v>
+      </c>
+      <c r="C24">
+        <v>9.797689059620801</v>
+      </c>
+      <c r="D24">
+        <v>12.1100890596208</v>
+      </c>
+      <c r="E24">
+        <v>-5.191600000000001</v>
+      </c>
+      <c r="F24">
+        <v>2.4684</v>
+      </c>
+      <c r="G24">
+        <v>0.156</v>
+      </c>
+      <c r="H24">
+        <v>3.56</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K24">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L24">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M24">
+        <v>0.1320594</v>
+      </c>
+      <c r="N24">
+        <v>0.4136072666666667</v>
+      </c>
+      <c r="O24">
+        <v>0.09099359866666668</v>
+      </c>
+      <c r="P24">
+        <v>0.322613668</v>
+      </c>
+      <c r="Q24">
+        <v>0.353613668</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1173916162676231</v>
+      </c>
+      <c r="T24">
+        <v>1.064255868097376</v>
+      </c>
+      <c r="U24">
+        <v>0.0535</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.04173</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.131978993291403</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1011180181020339</v>
+      </c>
+      <c r="C25">
+        <v>9.613207598520297</v>
+      </c>
+      <c r="D25">
+        <v>12.0378075985203</v>
+      </c>
+      <c r="E25">
+        <v>-5.079400000000001</v>
+      </c>
+      <c r="F25">
+        <v>2.5806</v>
+      </c>
+      <c r="G25">
+        <v>0.156</v>
+      </c>
+      <c r="H25">
+        <v>3.56</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K25">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L25">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M25">
+        <v>0.14502972</v>
+      </c>
+      <c r="N25">
+        <v>0.4006369466666667</v>
+      </c>
+      <c r="O25">
+        <v>0.08814012826666667</v>
+      </c>
+      <c r="P25">
+        <v>0.3124968184</v>
+      </c>
+      <c r="Q25">
+        <v>0.3434968184</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1182282313013427</v>
+      </c>
+      <c r="T25">
+        <v>1.075584970376463</v>
+      </c>
+      <c r="U25">
+        <v>0.0562</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.043836</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.76244721886429</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1010266555153218</v>
+      </c>
+      <c r="C26">
+        <v>9.518681780612127</v>
+      </c>
+      <c r="D26">
+        <v>12.05548178061213</v>
+      </c>
+      <c r="E26">
+        <v>-4.967200000000001</v>
+      </c>
+      <c r="F26">
+        <v>2.6928</v>
+      </c>
+      <c r="G26">
+        <v>0.156</v>
+      </c>
+      <c r="H26">
+        <v>3.56</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K26">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L26">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M26">
+        <v>0.15133536</v>
+      </c>
+      <c r="N26">
+        <v>0.3943313066666667</v>
+      </c>
+      <c r="O26">
+        <v>0.08675288746666668</v>
+      </c>
+      <c r="P26">
+        <v>0.3075784192000001</v>
+      </c>
+      <c r="Q26">
+        <v>0.3385784192</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1190868625201602</v>
+      </c>
+      <c r="T26">
+        <v>1.087212206926051</v>
+      </c>
+      <c r="U26">
+        <v>0.0562</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.043836</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.605678584744945</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1018517929286097</v>
+      </c>
+      <c r="C27">
+        <v>9.24871578236912</v>
+      </c>
+      <c r="D27">
+        <v>11.89771578236912</v>
+      </c>
+      <c r="E27">
+        <v>-4.855</v>
+      </c>
+      <c r="F27">
+        <v>2.805</v>
+      </c>
+      <c r="G27">
+        <v>0.156</v>
+      </c>
+      <c r="H27">
+        <v>3.56</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K27">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L27">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M27">
+        <v>0.1708245</v>
+      </c>
+      <c r="N27">
+        <v>0.3748421666666667</v>
+      </c>
+      <c r="O27">
+        <v>0.08246527666666667</v>
+      </c>
+      <c r="P27">
+        <v>0.29237689</v>
+      </c>
+      <c r="Q27">
+        <v>0.32337689</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1199683905714796</v>
+      </c>
+      <c r="T27">
+        <v>1.099149503116962</v>
+      </c>
+      <c r="U27">
+        <v>0.0609</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.047502</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.194311510741531</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1017970903418976</v>
+      </c>
+      <c r="C28">
+        <v>9.146846986964903</v>
+      </c>
+      <c r="D28">
+        <v>11.9080469869649</v>
+      </c>
+      <c r="E28">
+        <v>-4.742800000000001</v>
+      </c>
+      <c r="F28">
+        <v>2.9172</v>
+      </c>
+      <c r="G28">
+        <v>0.156</v>
+      </c>
+      <c r="H28">
+        <v>3.56</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K28">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L28">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M28">
+        <v>0.17765748</v>
+      </c>
+      <c r="N28">
+        <v>0.3680091866666667</v>
+      </c>
+      <c r="O28">
+        <v>0.08096202106666668</v>
+      </c>
+      <c r="P28">
+        <v>0.2870471656</v>
+      </c>
+      <c r="Q28">
+        <v>0.3180471656</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.120873743705267</v>
+      </c>
+      <c r="T28">
+        <v>1.111409428934655</v>
+      </c>
+      <c r="U28">
+        <v>0.0609</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.047502</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>3.07145337571301</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1037009677551855</v>
+      </c>
+      <c r="C29">
+        <v>8.685323048061973</v>
+      </c>
+      <c r="D29">
+        <v>11.55872304806197</v>
+      </c>
+      <c r="E29">
+        <v>-4.630600000000001</v>
+      </c>
+      <c r="F29">
+        <v>3.0294</v>
+      </c>
+      <c r="G29">
+        <v>0.156</v>
+      </c>
+      <c r="H29">
+        <v>3.56</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K29">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L29">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M29">
+        <v>0.21266388</v>
+      </c>
+      <c r="N29">
+        <v>0.3330027866666667</v>
+      </c>
+      <c r="O29">
+        <v>0.07326061306666667</v>
+      </c>
+      <c r="P29">
+        <v>0.2597421736000001</v>
+      </c>
+      <c r="Q29">
+        <v>0.2907421736</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1218039010345006</v>
+      </c>
+      <c r="T29">
+        <v>1.124005243130914</v>
+      </c>
+      <c r="U29">
+        <v>0.0702</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.054756</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.565864342673832</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1047452851684734</v>
+      </c>
+      <c r="C30">
+        <v>8.390077729149104</v>
+      </c>
+      <c r="D30">
+        <v>11.3756777291491</v>
+      </c>
+      <c r="E30">
+        <v>-4.518400000000001</v>
+      </c>
+      <c r="F30">
+        <v>3.1416</v>
+      </c>
+      <c r="G30">
+        <v>0.156</v>
+      </c>
+      <c r="H30">
+        <v>3.56</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K30">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L30">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M30">
+        <v>0.23530584</v>
+      </c>
+      <c r="N30">
+        <v>0.3103608266666668</v>
+      </c>
+      <c r="O30">
+        <v>0.06827938186666668</v>
+      </c>
+      <c r="P30">
+        <v>0.2420814448000001</v>
+      </c>
+      <c r="Q30">
+        <v>0.2730814448000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1227598960673241</v>
+      </c>
+      <c r="T30">
+        <v>1.136950941054848</v>
+      </c>
+      <c r="U30">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.31896780235742</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1047997825817612</v>
+      </c>
+      <c r="C31">
+        <v>8.268484591984338</v>
+      </c>
+      <c r="D31">
+        <v>11.36628459198434</v>
+      </c>
+      <c r="E31">
+        <v>-4.406200000000001</v>
+      </c>
+      <c r="F31">
+        <v>3.2538</v>
+      </c>
+      <c r="G31">
+        <v>0.156</v>
+      </c>
+      <c r="H31">
+        <v>3.56</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K31">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L31">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M31">
+        <v>0.24370962</v>
+      </c>
+      <c r="N31">
+        <v>0.3019570466666668</v>
+      </c>
+      <c r="O31">
+        <v>0.06643055026666669</v>
+      </c>
+      <c r="P31">
+        <v>0.2355264964000001</v>
+      </c>
+      <c r="Q31">
+        <v>0.2665264964</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1237428205376919</v>
+      </c>
+      <c r="T31">
+        <v>1.150261306525934</v>
+      </c>
+      <c r="U31">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.239003395379578</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1048542799950491</v>
+      </c>
+      <c r="C32">
+        <v>8.146906954244532</v>
+      </c>
+      <c r="D32">
+        <v>11.35690695424453</v>
+      </c>
+      <c r="E32">
+        <v>-4.294</v>
+      </c>
+      <c r="F32">
+        <v>3.366</v>
+      </c>
+      <c r="G32">
+        <v>0.156</v>
+      </c>
+      <c r="H32">
+        <v>3.56</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K32">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L32">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M32">
+        <v>0.2521134</v>
+      </c>
+      <c r="N32">
+        <v>0.2935532666666668</v>
+      </c>
+      <c r="O32">
+        <v>0.06458171866666669</v>
+      </c>
+      <c r="P32">
+        <v>0.2289715480000001</v>
+      </c>
+      <c r="Q32">
+        <v>0.2599715480000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1247538285643559</v>
+      </c>
+      <c r="T32">
+        <v>1.163951968153337</v>
+      </c>
+      <c r="U32">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.164369948866926</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.104908777408337</v>
+      </c>
+      <c r="C33">
+        <v>8.025344777598388</v>
+      </c>
+      <c r="D33">
+        <v>11.34754477759839</v>
+      </c>
+      <c r="E33">
+        <v>-4.181800000000001</v>
+      </c>
+      <c r="F33">
+        <v>3.4782</v>
+      </c>
+      <c r="G33">
+        <v>0.156</v>
+      </c>
+      <c r="H33">
+        <v>3.56</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K33">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L33">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M33">
+        <v>0.26051718</v>
+      </c>
+      <c r="N33">
+        <v>0.2851494866666667</v>
+      </c>
+      <c r="O33">
+        <v>0.06273288706666669</v>
+      </c>
+      <c r="P33">
+        <v>0.2224165996</v>
+      </c>
+      <c r="Q33">
+        <v>0.2534165996</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1257941411715029</v>
+      </c>
+      <c r="T33">
+        <v>1.178039460552548</v>
+      </c>
+      <c r="U33">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.094551563419605</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1049632748216249</v>
+      </c>
+      <c r="C34">
+        <v>7.903798023840885</v>
+      </c>
+      <c r="D34">
+        <v>11.33819802384089</v>
+      </c>
+      <c r="E34">
+        <v>-4.069600000000001</v>
+      </c>
+      <c r="F34">
+        <v>3.5904</v>
+      </c>
+      <c r="G34">
+        <v>0.156</v>
+      </c>
+      <c r="H34">
+        <v>3.56</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K34">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L34">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M34">
+        <v>0.26892096</v>
+      </c>
+      <c r="N34">
+        <v>0.2767457066666668</v>
+      </c>
+      <c r="O34">
+        <v>0.06088405546666668</v>
+      </c>
+      <c r="P34">
+        <v>0.2158616512000001</v>
+      </c>
+      <c r="Q34">
+        <v>0.2468616512</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.126865051208272</v>
+      </c>
+      <c r="T34">
+        <v>1.192541290963502</v>
+      </c>
+      <c r="U34">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.029096827062743</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1092133922349128</v>
+      </c>
+      <c r="C35">
+        <v>7.107230017600456</v>
+      </c>
+      <c r="D35">
+        <v>10.65383001760046</v>
+      </c>
+      <c r="E35">
+        <v>-3.957400000000001</v>
+      </c>
+      <c r="F35">
+        <v>3.7026</v>
+      </c>
+      <c r="G35">
+        <v>0.156</v>
+      </c>
+      <c r="H35">
+        <v>3.56</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K35">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L35">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M35">
+        <v>0.3376771200000001</v>
+      </c>
+      <c r="N35">
+        <v>0.2079895466666667</v>
+      </c>
+      <c r="O35">
+        <v>0.04575770026666667</v>
+      </c>
+      <c r="P35">
+        <v>0.1622318464</v>
+      </c>
+      <c r="Q35">
+        <v>0.1932318464</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1279679287088251</v>
+      </c>
+      <c r="T35">
+        <v>1.207476011834483</v>
+      </c>
+      <c r="U35">
+        <v>0.0912</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.071136</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>1.615942077054752</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1093950296482007</v>
+      </c>
+      <c r="C36">
+        <v>6.967618255955912</v>
+      </c>
+      <c r="D36">
+        <v>10.62641825595591</v>
+      </c>
+      <c r="E36">
+        <v>-3.845200000000001</v>
+      </c>
+      <c r="F36">
+        <v>3.8148</v>
+      </c>
+      <c r="G36">
+        <v>0.156</v>
+      </c>
+      <c r="H36">
+        <v>3.56</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K36">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L36">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M36">
+        <v>0.3479097600000001</v>
+      </c>
+      <c r="N36">
+        <v>0.1977569066666667</v>
+      </c>
+      <c r="O36">
+        <v>0.04350651946666667</v>
+      </c>
+      <c r="P36">
+        <v>0.1542503872</v>
+      </c>
+      <c r="Q36">
+        <v>0.1852503872</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1291042267396981</v>
+      </c>
+      <c r="T36">
+        <v>1.222863300004586</v>
+      </c>
+      <c r="U36">
+        <v>0.0912</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.071136</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.568414368906083</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1095766670614886</v>
+      </c>
+      <c r="C37">
+        <v>6.828147190438654</v>
+      </c>
+      <c r="D37">
+        <v>10.59914719043865</v>
+      </c>
+      <c r="E37">
+        <v>-3.733000000000001</v>
+      </c>
+      <c r="F37">
+        <v>3.927</v>
+      </c>
+      <c r="G37">
+        <v>0.156</v>
+      </c>
+      <c r="H37">
+        <v>3.56</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K37">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L37">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M37">
+        <v>0.3581424000000001</v>
+      </c>
+      <c r="N37">
+        <v>0.1875242666666667</v>
+      </c>
+      <c r="O37">
+        <v>0.04125533866666667</v>
+      </c>
+      <c r="P37">
+        <v>0.146268928</v>
+      </c>
+      <c r="Q37">
+        <v>0.177268928</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1302754877869056</v>
+      </c>
+      <c r="T37">
+        <v>1.238724043195307</v>
+      </c>
+      <c r="U37">
+        <v>0.0912</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.071136</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.52360252979448</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1305267019822033</v>
+      </c>
+      <c r="C38">
+        <v>4.29514170009663</v>
+      </c>
+      <c r="D38">
+        <v>8.178341700096629</v>
+      </c>
+      <c r="E38">
+        <v>-3.620800000000001</v>
+      </c>
+      <c r="F38">
+        <v>4.0392</v>
+      </c>
+      <c r="G38">
+        <v>0.156</v>
+      </c>
+      <c r="H38">
+        <v>3.56</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K38">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L38">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M38">
+        <v>0.6325387200000001</v>
+      </c>
+      <c r="N38">
+        <v>-0.08687205333333337</v>
+      </c>
+      <c r="O38">
+        <v>-0.01911185173333334</v>
+      </c>
+      <c r="P38">
+        <v>-0.06776020160000003</v>
+      </c>
+      <c r="Q38">
+        <v>-0.03676020160000006</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1325782006053625</v>
+      </c>
+      <c r="T38">
+        <v>1.269906448469182</v>
+      </c>
+      <c r="U38">
+        <v>0.1566</v>
+      </c>
+      <c r="V38">
+        <v>0.1897854832770817</v>
+      </c>
+      <c r="W38">
+        <v>0.126879593318809</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.8626612876230986</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1317047019822033</v>
+      </c>
+      <c r="C39">
+        <v>4.079243110927705</v>
+      </c>
+      <c r="D39">
+        <v>8.074643110927704</v>
+      </c>
+      <c r="E39">
+        <v>-3.508600000000001</v>
+      </c>
+      <c r="F39">
+        <v>4.1514</v>
+      </c>
+      <c r="G39">
+        <v>0.156</v>
+      </c>
+      <c r="H39">
+        <v>3.56</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K39">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L39">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M39">
+        <v>0.65010924</v>
+      </c>
+      <c r="N39">
+        <v>-0.1044425733333333</v>
+      </c>
+      <c r="O39">
+        <v>-0.02297736613333332</v>
+      </c>
+      <c r="P39">
+        <v>-0.08146520719999997</v>
+      </c>
+      <c r="Q39">
+        <v>-0.0504652072</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1340667434721143</v>
+      </c>
+      <c r="T39">
+        <v>1.290063693682979</v>
+      </c>
+      <c r="U39">
+        <v>0.1566</v>
+      </c>
+      <c r="V39">
+        <v>0.1846561458912147</v>
+      </c>
+      <c r="W39">
+        <v>0.1276828475534358</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.8393461176873394</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1328827019822033</v>
+      </c>
+      <c r="C40">
+        <v>3.865941320861427</v>
+      </c>
+      <c r="D40">
+        <v>7.973541320861427</v>
+      </c>
+      <c r="E40">
+        <v>-3.396400000000001</v>
+      </c>
+      <c r="F40">
+        <v>4.2636</v>
+      </c>
+      <c r="G40">
+        <v>0.156</v>
+      </c>
+      <c r="H40">
+        <v>3.56</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K40">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L40">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M40">
+        <v>0.6676797600000001</v>
+      </c>
+      <c r="N40">
+        <v>-0.1220130933333333</v>
+      </c>
+      <c r="O40">
+        <v>-0.02684288053333333</v>
+      </c>
+      <c r="P40">
+        <v>-0.09517021279999999</v>
+      </c>
+      <c r="Q40">
+        <v>-0.06417021280000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1356033038506968</v>
+      </c>
+      <c r="T40">
+        <v>1.310871172613349</v>
+      </c>
+      <c r="U40">
+        <v>0.1566</v>
+      </c>
+      <c r="V40">
+        <v>0.1797967736309195</v>
+      </c>
+      <c r="W40">
+        <v>0.128443825249398</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8172580619587251</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1555190292844484</v>
+      </c>
+      <c r="C41">
+        <v>2.207363731846953</v>
+      </c>
+      <c r="D41">
+        <v>6.427163731846954</v>
+      </c>
+      <c r="E41">
+        <v>-3.2842</v>
+      </c>
+      <c r="F41">
+        <v>4.375800000000001</v>
+      </c>
+      <c r="G41">
+        <v>0.156</v>
+      </c>
+      <c r="H41">
+        <v>3.56</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K41">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L41">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M41">
+        <v>0.9136670400000002</v>
+      </c>
+      <c r="N41">
+        <v>-0.3680003733333335</v>
+      </c>
+      <c r="O41">
+        <v>-0.08096008213333336</v>
+      </c>
+      <c r="P41">
+        <v>-0.2870402912000001</v>
+      </c>
+      <c r="Q41">
+        <v>-0.2560402912000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1389940585076674</v>
+      </c>
+      <c r="T41">
+        <v>1.356787400225607</v>
+      </c>
+      <c r="U41">
+        <v>0.2088</v>
+      </c>
+      <c r="V41">
+        <v>0.1313899499610565</v>
+      </c>
+      <c r="W41">
+        <v>0.1813657784481314</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5972270452775298</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1572190292844484</v>
+      </c>
+      <c r="C42">
+        <v>2.002896649350485</v>
+      </c>
+      <c r="D42">
+        <v>6.334896649350486</v>
+      </c>
+      <c r="E42">
+        <v>-3.172000000000001</v>
+      </c>
+      <c r="F42">
+        <v>4.488</v>
+      </c>
+      <c r="G42">
+        <v>0.156</v>
+      </c>
+      <c r="H42">
+        <v>3.56</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K42">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L42">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M42">
+        <v>0.9370944000000001</v>
+      </c>
+      <c r="N42">
+        <v>-0.3914277333333334</v>
+      </c>
+      <c r="O42">
+        <v>-0.08611410133333335</v>
+      </c>
+      <c r="P42">
+        <v>-0.305313632</v>
+      </c>
+      <c r="Q42">
+        <v>-0.274313632</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1406639594827952</v>
+      </c>
+      <c r="T42">
+        <v>1.379400523562701</v>
+      </c>
+      <c r="U42">
+        <v>0.2088</v>
+      </c>
+      <c r="V42">
+        <v>0.1281052012120301</v>
+      </c>
+      <c r="W42">
+        <v>0.1820516339869281</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5822963691455916</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1589190292844483</v>
+      </c>
+      <c r="C43">
+        <v>1.801041210340956</v>
+      </c>
+      <c r="D43">
+        <v>6.245241210340957</v>
+      </c>
+      <c r="E43">
+        <v>-3.0598</v>
+      </c>
+      <c r="F43">
+        <v>4.600200000000001</v>
+      </c>
+      <c r="G43">
+        <v>0.156</v>
+      </c>
+      <c r="H43">
+        <v>3.56</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K43">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L43">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M43">
+        <v>0.9605217600000002</v>
+      </c>
+      <c r="N43">
+        <v>-0.4148550933333335</v>
+      </c>
+      <c r="O43">
+        <v>-0.09126812053333337</v>
+      </c>
+      <c r="P43">
+        <v>-0.3235869728000001</v>
+      </c>
+      <c r="Q43">
+        <v>-0.2925869728000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1423904672706392</v>
+      </c>
+      <c r="T43">
+        <v>1.402780193453594</v>
+      </c>
+      <c r="U43">
+        <v>0.2088</v>
+      </c>
+      <c r="V43">
+        <v>0.1249806841092977</v>
+      </c>
+      <c r="W43">
+        <v>0.1827040331579786</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5680940186786259</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1606190292844484</v>
+      </c>
+      <c r="C44">
+        <v>1.601688077370333</v>
+      </c>
+      <c r="D44">
+        <v>6.158088077370333</v>
+      </c>
+      <c r="E44">
+        <v>-2.947600000000001</v>
+      </c>
+      <c r="F44">
+        <v>4.7124</v>
+      </c>
+      <c r="G44">
+        <v>0.156</v>
+      </c>
+      <c r="H44">
+        <v>3.56</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K44">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L44">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M44">
+        <v>0.98394912</v>
+      </c>
+      <c r="N44">
+        <v>-0.4382824533333333</v>
+      </c>
+      <c r="O44">
+        <v>-0.09642213973333331</v>
+      </c>
+      <c r="P44">
+        <v>-0.3418603136</v>
+      </c>
+      <c r="Q44">
+        <v>-0.3108603136</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1441765098097881</v>
+      </c>
+      <c r="T44">
+        <v>1.426966058857966</v>
+      </c>
+      <c r="U44">
+        <v>0.2088</v>
+      </c>
+      <c r="V44">
+        <v>0.1220049535352668</v>
+      </c>
+      <c r="W44">
+        <v>0.1833253657018363</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5545679706148492</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1623190292844484</v>
+      </c>
+      <c r="C45">
+        <v>1.404733932262688</v>
+      </c>
+      <c r="D45">
+        <v>6.073333932262688</v>
+      </c>
+      <c r="E45">
+        <v>-2.835400000000001</v>
+      </c>
+      <c r="F45">
+        <v>4.8246</v>
+      </c>
+      <c r="G45">
+        <v>0.156</v>
+      </c>
+      <c r="H45">
+        <v>3.56</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K45">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L45">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M45">
+        <v>1.00737648</v>
+      </c>
+      <c r="N45">
+        <v>-0.4617098133333333</v>
+      </c>
+      <c r="O45">
+        <v>-0.1015761589333333</v>
+      </c>
+      <c r="P45">
+        <v>-0.3601336543999999</v>
+      </c>
+      <c r="Q45">
+        <v>-0.3291336544</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1460252205082054</v>
+      </c>
+      <c r="T45">
+        <v>1.452000551118632</v>
+      </c>
+      <c r="U45">
+        <v>0.2088</v>
+      </c>
+      <c r="V45">
+        <v>0.1191676290344467</v>
+      </c>
+      <c r="W45">
+        <v>0.1839177990576076</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5416710410656667</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1640190292844484</v>
+      </c>
+      <c r="C46">
+        <v>1.210081067519639</v>
+      </c>
+      <c r="D46">
+        <v>5.99088106751964</v>
+      </c>
+      <c r="E46">
+        <v>-2.7232</v>
+      </c>
+      <c r="F46">
+        <v>4.936800000000001</v>
+      </c>
+      <c r="G46">
+        <v>0.156</v>
+      </c>
+      <c r="H46">
+        <v>3.56</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K46">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L46">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M46">
+        <v>1.03080384</v>
+      </c>
+      <c r="N46">
+        <v>-0.4851371733333334</v>
+      </c>
+      <c r="O46">
+        <v>-0.1067301781333334</v>
+      </c>
+      <c r="P46">
+        <v>-0.3784069952</v>
+      </c>
+      <c r="Q46">
+        <v>-0.3474069952000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1479399565887091</v>
+      </c>
+      <c r="T46">
+        <v>1.477929132388608</v>
+      </c>
+      <c r="U46">
+        <v>0.2088</v>
+      </c>
+      <c r="V46">
+        <v>0.1164592738291183</v>
+      </c>
+      <c r="W46">
+        <v>0.1844833036244801</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5293603355869014</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1657190292844484</v>
+      </c>
+      <c r="C47">
+        <v>1.017637010562993</v>
+      </c>
+      <c r="D47">
+        <v>5.910637010562994</v>
+      </c>
+      <c r="E47">
+        <v>-2.611000000000001</v>
+      </c>
+      <c r="F47">
+        <v>5.049</v>
+      </c>
+      <c r="G47">
+        <v>0.156</v>
+      </c>
+      <c r="H47">
+        <v>3.56</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K47">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L47">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M47">
+        <v>1.0542312</v>
+      </c>
+      <c r="N47">
+        <v>-0.5085645333333335</v>
+      </c>
+      <c r="O47">
+        <v>-0.1118841973333334</v>
+      </c>
+      <c r="P47">
+        <v>-0.3966803360000001</v>
+      </c>
+      <c r="Q47">
+        <v>-0.3656803360000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1499243194357766</v>
+      </c>
+      <c r="T47">
+        <v>1.50480057115931</v>
+      </c>
+      <c r="U47">
+        <v>0.2088</v>
+      </c>
+      <c r="V47">
+        <v>0.113871289966249</v>
+      </c>
+      <c r="W47">
+        <v>0.1850236746550472</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5175967725738592</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1674190292844484</v>
+      </c>
+      <c r="C48">
+        <v>0.8273141777764454</v>
+      </c>
+      <c r="D48">
+        <v>5.832514177776447</v>
+      </c>
+      <c r="E48">
+        <v>-2.4988</v>
+      </c>
+      <c r="F48">
+        <v>5.161200000000001</v>
+      </c>
+      <c r="G48">
+        <v>0.156</v>
+      </c>
+      <c r="H48">
+        <v>3.56</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K48">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L48">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M48">
+        <v>1.07765856</v>
+      </c>
+      <c r="N48">
+        <v>-0.5319918933333334</v>
+      </c>
+      <c r="O48">
+        <v>-0.1170382165333334</v>
+      </c>
+      <c r="P48">
+        <v>-0.4149536768000001</v>
+      </c>
+      <c r="Q48">
+        <v>-0.3839536768000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1519821772031058</v>
+      </c>
+      <c r="T48">
+        <v>1.532667248403001</v>
+      </c>
+      <c r="U48">
+        <v>0.2088</v>
+      </c>
+      <c r="V48">
+        <v>0.1113958271408958</v>
+      </c>
+      <c r="W48">
+        <v>0.185540551292981</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5063446688222535</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1836337255038875</v>
+      </c>
+      <c r="C49">
+        <v>0.06214163799545158</v>
+      </c>
+      <c r="D49">
+        <v>5.179541637995452</v>
+      </c>
+      <c r="E49">
+        <v>-2.3866</v>
+      </c>
+      <c r="F49">
+        <v>5.273400000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.156</v>
+      </c>
+      <c r="H49">
+        <v>3.56</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K49">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L49">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M49">
+        <v>1.25928792</v>
+      </c>
+      <c r="N49">
+        <v>-0.7136212533333335</v>
+      </c>
+      <c r="O49">
+        <v>-0.1569966757333334</v>
+      </c>
+      <c r="P49">
+        <v>-0.5566245776000001</v>
+      </c>
+      <c r="Q49">
+        <v>-0.5256245776000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1549001356775778</v>
+      </c>
+      <c r="T49">
+        <v>1.572181061412603</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.09532900678239387</v>
+      </c>
+      <c r="W49">
+        <v>0.2160354331803644</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4333136671926994</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1856337255038875</v>
+      </c>
+      <c r="C50">
+        <v>-0.1206081164321615</v>
+      </c>
+      <c r="D50">
+        <v>5.108991883567839</v>
+      </c>
+      <c r="E50">
+        <v>-2.274400000000001</v>
+      </c>
+      <c r="F50">
+        <v>5.3856</v>
+      </c>
+      <c r="G50">
+        <v>0.156</v>
+      </c>
+      <c r="H50">
+        <v>3.56</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K50">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L50">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M50">
+        <v>1.28608128</v>
+      </c>
+      <c r="N50">
+        <v>-0.7404146133333334</v>
+      </c>
+      <c r="O50">
+        <v>-0.1628912149333333</v>
+      </c>
+      <c r="P50">
+        <v>-0.5775233984</v>
+      </c>
+      <c r="Q50">
+        <v>-0.5465233984</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1571328305944542</v>
+      </c>
+      <c r="T50">
+        <v>1.602415312593615</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.09334298580776067</v>
+      </c>
+      <c r="W50">
+        <v>0.2165096949891068</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4242862991261849</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1876337255038874</v>
+      </c>
+      <c r="C51">
+        <v>-0.3014618018286788</v>
+      </c>
+      <c r="D51">
+        <v>5.040338198171321</v>
+      </c>
+      <c r="E51">
+        <v>-2.162200000000001</v>
+      </c>
+      <c r="F51">
+        <v>5.4978</v>
+      </c>
+      <c r="G51">
+        <v>0.156</v>
+      </c>
+      <c r="H51">
+        <v>3.56</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K51">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L51">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M51">
+        <v>1.31287464</v>
+      </c>
+      <c r="N51">
+        <v>-0.7672079733333332</v>
+      </c>
+      <c r="O51">
+        <v>-0.1687857541333333</v>
+      </c>
+      <c r="P51">
+        <v>-0.5984222191999999</v>
+      </c>
+      <c r="Q51">
+        <v>-0.5674222192</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1594530821747376</v>
+      </c>
+      <c r="T51">
+        <v>1.633835220683686</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.09143802691372475</v>
+      </c>
+      <c r="W51">
+        <v>0.2169645991730025</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4156273950623852</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1896337255038875</v>
+      </c>
+      <c r="C52">
+        <v>-0.480494841738464</v>
+      </c>
+      <c r="D52">
+        <v>4.973505158261537</v>
+      </c>
+      <c r="E52">
+        <v>-2.050000000000001</v>
+      </c>
+      <c r="F52">
+        <v>5.61</v>
+      </c>
+      <c r="G52">
+        <v>0.156</v>
+      </c>
+      <c r="H52">
+        <v>3.56</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K52">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L52">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M52">
+        <v>1.339668</v>
+      </c>
+      <c r="N52">
+        <v>-0.7940013333333333</v>
+      </c>
+      <c r="O52">
+        <v>-0.1746802933333333</v>
+      </c>
+      <c r="P52">
+        <v>-0.61932104</v>
+      </c>
+      <c r="Q52">
+        <v>-0.5883210400000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1618661438182324</v>
+      </c>
+      <c r="T52">
+        <v>1.66651192509736</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.08960926637545025</v>
+      </c>
+      <c r="W52">
+        <v>0.2174013071895425</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4073148471611374</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1916337255038875</v>
+      </c>
+      <c r="C53">
+        <v>-0.6577787117005949</v>
+      </c>
+      <c r="D53">
+        <v>4.908421288299406</v>
+      </c>
+      <c r="E53">
+        <v>-1.9378</v>
+      </c>
+      <c r="F53">
+        <v>5.722200000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.156</v>
+      </c>
+      <c r="H53">
+        <v>3.56</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K53">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L53">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M53">
+        <v>1.36646136</v>
+      </c>
+      <c r="N53">
+        <v>-0.8207946933333334</v>
+      </c>
+      <c r="O53">
+        <v>-0.1805748325333334</v>
+      </c>
+      <c r="P53">
+        <v>-0.6402198608</v>
+      </c>
+      <c r="Q53">
+        <v>-0.6092198608000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1643776977737065</v>
+      </c>
+      <c r="T53">
+        <v>1.700522372548326</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.08785222193671592</v>
+      </c>
+      <c r="W53">
+        <v>0.2178208894015123</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3993282815305269</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1936337255038875</v>
+      </c>
+      <c r="C54">
+        <v>-0.8333811942324276</v>
+      </c>
+      <c r="D54">
+        <v>4.845018805767573</v>
+      </c>
+      <c r="E54">
+        <v>-1.825600000000001</v>
+      </c>
+      <c r="F54">
+        <v>5.8344</v>
+      </c>
+      <c r="G54">
+        <v>0.156</v>
+      </c>
+      <c r="H54">
+        <v>3.56</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K54">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L54">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M54">
+        <v>1.39325472</v>
+      </c>
+      <c r="N54">
+        <v>-0.8475880533333335</v>
+      </c>
+      <c r="O54">
+        <v>-0.1864693717333334</v>
+      </c>
+      <c r="P54">
+        <v>-0.6611186816000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.6301186816000002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1669938998106588</v>
+      </c>
+      <c r="T54">
+        <v>1.735949921976417</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0861627561302406</v>
+      </c>
+      <c r="W54">
+        <v>0.2182243338360985</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3916488915010937</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1956337255038875</v>
+      </c>
+      <c r="C55">
+        <v>-1.007366614303286</v>
+      </c>
+      <c r="D55">
+        <v>4.783233385696716</v>
+      </c>
+      <c r="E55">
+        <v>-1.7134</v>
+      </c>
+      <c r="F55">
+        <v>5.946600000000001</v>
+      </c>
+      <c r="G55">
+        <v>0.156</v>
+      </c>
+      <c r="H55">
+        <v>3.56</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K55">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L55">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M55">
+        <v>1.42004808</v>
+      </c>
+      <c r="N55">
+        <v>-0.8743814133333336</v>
+      </c>
+      <c r="O55">
+        <v>-0.1923639109333334</v>
+      </c>
+      <c r="P55">
+        <v>-0.6820175024000003</v>
+      </c>
+      <c r="Q55">
+        <v>-0.6510175024000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1697214295938643</v>
+      </c>
+      <c r="T55">
+        <v>1.772885026699319</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.08453704375042474</v>
+      </c>
+      <c r="W55">
+        <v>0.2186125539523986</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.384259289774658</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1976337255038875</v>
+      </c>
+      <c r="C56">
+        <v>-1.179796057017952</v>
+      </c>
+      <c r="D56">
+        <v>4.723003942982049</v>
+      </c>
+      <c r="E56">
+        <v>-1.6012</v>
+      </c>
+      <c r="F56">
+        <v>6.058800000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.156</v>
+      </c>
+      <c r="H56">
+        <v>3.56</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K56">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L56">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M56">
+        <v>1.44684144</v>
+      </c>
+      <c r="N56">
+        <v>-0.9011747733333335</v>
+      </c>
+      <c r="O56">
+        <v>-0.1982584501333334</v>
+      </c>
+      <c r="P56">
+        <v>-0.7029163232000002</v>
+      </c>
+      <c r="Q56">
+        <v>-0.6719163232000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1725675476285135</v>
+      </c>
+      <c r="T56">
+        <v>1.811426005540608</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.08297154294023169</v>
+      </c>
+      <c r="W56">
+        <v>0.2189863955458727</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3771433770010532</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1996337255038875</v>
+      </c>
+      <c r="C57">
+        <v>-1.35072756905854</v>
+      </c>
+      <c r="D57">
+        <v>4.664272430941462</v>
+      </c>
+      <c r="E57">
+        <v>-1.489</v>
+      </c>
+      <c r="F57">
+        <v>6.171000000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.156</v>
+      </c>
+      <c r="H57">
+        <v>3.56</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K57">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L57">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M57">
+        <v>1.4736348</v>
+      </c>
+      <c r="N57">
+        <v>-0.9279681333333336</v>
+      </c>
+      <c r="O57">
+        <v>-0.2041529893333334</v>
+      </c>
+      <c r="P57">
+        <v>-0.7238151440000002</v>
+      </c>
+      <c r="Q57">
+        <v>-0.6928151440000003</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.175540159798036</v>
+      </c>
+      <c r="T57">
+        <v>1.851679916774844</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.08146296943222749</v>
+      </c>
+      <c r="W57">
+        <v>0.2193466428995841</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3702862246919431</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2016337255038875</v>
+      </c>
+      <c r="C58">
+        <v>-1.520216345281129</v>
+      </c>
+      <c r="D58">
+        <v>4.606983654718872</v>
+      </c>
+      <c r="E58">
+        <v>-1.3768</v>
+      </c>
+      <c r="F58">
+        <v>6.283200000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.156</v>
+      </c>
+      <c r="H58">
+        <v>3.56</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K58">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L58">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M58">
+        <v>1.50042816</v>
+      </c>
+      <c r="N58">
+        <v>-0.9547614933333335</v>
+      </c>
+      <c r="O58">
+        <v>-0.2100475285333334</v>
+      </c>
+      <c r="P58">
+        <v>-0.7447139648000001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.7137139648000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1786478907025368</v>
+      </c>
+      <c r="T58">
+        <v>1.893763551247</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.08000827354950914</v>
+      </c>
+      <c r="W58">
+        <v>0.2196940242763772</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.363673970679587</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2036337255038875</v>
+      </c>
+      <c r="C59">
+        <v>-1.688314901728066</v>
+      </c>
+      <c r="D59">
+        <v>4.551085098271936</v>
+      </c>
+      <c r="E59">
+        <v>-1.2646</v>
+      </c>
+      <c r="F59">
+        <v>6.395400000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.156</v>
+      </c>
+      <c r="H59">
+        <v>3.56</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K59">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L59">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M59">
+        <v>1.52722152</v>
+      </c>
+      <c r="N59">
+        <v>-0.9815548533333336</v>
+      </c>
+      <c r="O59">
+        <v>-0.2159420677333334</v>
+      </c>
+      <c r="P59">
+        <v>-0.7656127856000002</v>
+      </c>
+      <c r="Q59">
+        <v>-0.7346127856000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1819001672305028</v>
+      </c>
+      <c r="T59">
+        <v>1.937804564066697</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.07860461962758793</v>
+      </c>
+      <c r="W59">
+        <v>0.220029216832932</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3572937255799451</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2056337255038874</v>
+      </c>
+      <c r="C60">
+        <v>-1.855073236195826</v>
+      </c>
+      <c r="D60">
+        <v>4.496526763804174</v>
+      </c>
+      <c r="E60">
+        <v>-1.152400000000001</v>
+      </c>
+      <c r="F60">
+        <v>6.5076</v>
+      </c>
+      <c r="G60">
+        <v>0.156</v>
+      </c>
+      <c r="H60">
+        <v>3.56</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K60">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L60">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M60">
+        <v>1.55401488</v>
+      </c>
+      <c r="N60">
+        <v>-1.008348213333333</v>
+      </c>
+      <c r="O60">
+        <v>-0.2218366069333333</v>
+      </c>
+      <c r="P60">
+        <v>-0.7865116064</v>
+      </c>
+      <c r="Q60">
+        <v>-0.7555116064</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1853073140693243</v>
+      </c>
+      <c r="T60">
+        <v>1.983942767973047</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.07724936756504332</v>
+      </c>
+      <c r="W60">
+        <v>0.2203528510254677</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3511334889320151</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2076337255038874</v>
+      </c>
+      <c r="C61">
+        <v>-2.020538977390414</v>
+      </c>
+      <c r="D61">
+        <v>4.443261022609586</v>
+      </c>
+      <c r="E61">
+        <v>-1.040200000000001</v>
+      </c>
+      <c r="F61">
+        <v>6.6198</v>
+      </c>
+      <c r="G61">
+        <v>0.156</v>
+      </c>
+      <c r="H61">
+        <v>3.56</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K61">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L61">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M61">
+        <v>1.58080824</v>
+      </c>
+      <c r="N61">
+        <v>-1.035141573333333</v>
+      </c>
+      <c r="O61">
+        <v>-0.2277311461333333</v>
+      </c>
+      <c r="P61">
+        <v>-0.8074104272</v>
+      </c>
+      <c r="Q61">
+        <v>-0.7764104272000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1888806631929663</v>
+      </c>
+      <c r="T61">
+        <v>2.032331615972389</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.07594005625038157</v>
+      </c>
+      <c r="W61">
+        <v>0.2206655145674089</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3451820738653707</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2096337255038874</v>
+      </c>
+      <c r="C62">
+        <v>-2.184757523605501</v>
+      </c>
+      <c r="D62">
+        <v>4.3912424763945</v>
+      </c>
+      <c r="E62">
+        <v>-0.9280000000000008</v>
+      </c>
+      <c r="F62">
+        <v>6.732</v>
+      </c>
+      <c r="G62">
+        <v>0.156</v>
+      </c>
+      <c r="H62">
+        <v>3.56</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K62">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L62">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M62">
+        <v>1.6076016</v>
+      </c>
+      <c r="N62">
+        <v>-1.061934933333333</v>
+      </c>
+      <c r="O62">
+        <v>-0.2336256853333334</v>
+      </c>
+      <c r="P62">
+        <v>-0.8283092480000001</v>
+      </c>
+      <c r="Q62">
+        <v>-0.7973092480000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1926326797727905</v>
+      </c>
+      <c r="T62">
+        <v>2.083139906371699</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07467438864620853</v>
+      </c>
+      <c r="W62">
+        <v>0.2209677559912854</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3394290393009479</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2116337255038875</v>
+      </c>
+      <c r="C63">
+        <v>-2.347772171772021</v>
+      </c>
+      <c r="D63">
+        <v>4.34042782822798</v>
+      </c>
+      <c r="E63">
+        <v>-0.8158000000000012</v>
+      </c>
+      <c r="F63">
+        <v>6.8442</v>
+      </c>
+      <c r="G63">
+        <v>0.156</v>
+      </c>
+      <c r="H63">
+        <v>3.56</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K63">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L63">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M63">
+        <v>1.63439496</v>
+      </c>
+      <c r="N63">
+        <v>-1.088728293333333</v>
+      </c>
+      <c r="O63">
+        <v>-0.2395202245333333</v>
+      </c>
+      <c r="P63">
+        <v>-0.8492080688</v>
+      </c>
+      <c r="Q63">
+        <v>-0.8182080688</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1965771074592723</v>
+      </c>
+      <c r="T63">
+        <v>2.13655375012482</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07345021834053299</v>
+      </c>
+      <c r="W63">
+        <v>0.2212600878602807</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3338646288206045</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2136337255038875</v>
+      </c>
+      <c r="C64">
+        <v>-2.509624237650254</v>
+      </c>
+      <c r="D64">
+        <v>4.290775762349747</v>
+      </c>
+      <c r="E64">
+        <v>-0.7036000000000007</v>
+      </c>
+      <c r="F64">
+        <v>6.9564</v>
+      </c>
+      <c r="G64">
+        <v>0.156</v>
+      </c>
+      <c r="H64">
+        <v>3.56</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K64">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L64">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M64">
+        <v>1.66118832</v>
+      </c>
+      <c r="N64">
+        <v>-1.115521653333333</v>
+      </c>
+      <c r="O64">
+        <v>-0.2454147637333333</v>
+      </c>
+      <c r="P64">
+        <v>-0.8701068896</v>
+      </c>
+      <c r="Q64">
+        <v>-0.8391068896</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2007291366029374</v>
+      </c>
+      <c r="T64">
+        <v>2.192778848812315</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.07226553739955664</v>
+      </c>
+      <c r="W64">
+        <v>0.2215429896689859</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3284797154525302</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2156337255038875</v>
+      </c>
+      <c r="C65">
+        <v>-2.67035316786561</v>
+      </c>
+      <c r="D65">
+        <v>4.242246832134391</v>
+      </c>
+      <c r="E65">
+        <v>-0.5914000000000001</v>
+      </c>
+      <c r="F65">
+        <v>7.068600000000001</v>
+      </c>
+      <c r="G65">
+        <v>0.156</v>
+      </c>
+      <c r="H65">
+        <v>3.56</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K65">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L65">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M65">
+        <v>1.68798168</v>
+      </c>
+      <c r="N65">
+        <v>-1.142315013333334</v>
+      </c>
+      <c r="O65">
+        <v>-0.2513093029333334</v>
+      </c>
+      <c r="P65">
+        <v>-0.8910057104000002</v>
+      </c>
+      <c r="Q65">
+        <v>-0.8600057104000003</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2051055997543681</v>
+      </c>
+      <c r="T65">
+        <v>2.252043142023459</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.07111846537734146</v>
+      </c>
+      <c r="W65">
+        <v>0.2218169104678909</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3232657517151885</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2176337255038874</v>
+      </c>
+      <c r="C66">
+        <v>-2.829996644426658</v>
+      </c>
+      <c r="D66">
+        <v>4.194803355573343</v>
+      </c>
+      <c r="E66">
+        <v>-0.4792000000000005</v>
+      </c>
+      <c r="F66">
+        <v>7.180800000000001</v>
+      </c>
+      <c r="G66">
+        <v>0.156</v>
+      </c>
+      <c r="H66">
+        <v>3.56</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K66">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L66">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M66">
+        <v>1.71477504</v>
+      </c>
+      <c r="N66">
+        <v>-1.169108373333333</v>
+      </c>
+      <c r="O66">
+        <v>-0.2572038421333334</v>
+      </c>
+      <c r="P66">
+        <v>-0.9119045312</v>
+      </c>
+      <c r="Q66">
+        <v>-0.8809045312000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.209725199747545</v>
+      </c>
+      <c r="T66">
+        <v>2.314599895968555</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07000723935582051</v>
+      </c>
+      <c r="W66">
+        <v>0.2220822712418301</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3182147243446386</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2196337255038875</v>
+      </c>
+      <c r="C67">
+        <v>-2.988590682307422</v>
+      </c>
+      <c r="D67">
+        <v>4.148409317692579</v>
+      </c>
+      <c r="E67">
+        <v>-0.367</v>
+      </c>
+      <c r="F67">
+        <v>7.293000000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.156</v>
+      </c>
+      <c r="H67">
+        <v>3.56</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K67">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L67">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M67">
+        <v>1.7415684</v>
+      </c>
+      <c r="N67">
+        <v>-1.195901733333333</v>
+      </c>
+      <c r="O67">
+        <v>-0.2630983813333334</v>
+      </c>
+      <c r="P67">
+        <v>-0.9328033520000001</v>
+      </c>
+      <c r="Q67">
+        <v>-0.9018033520000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2146087768831892</v>
+      </c>
+      <c r="T67">
+        <v>2.380731321567657</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.06893020490419249</v>
+      </c>
+      <c r="W67">
+        <v>0.2223394670688789</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3133191132008749</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2216337255038874</v>
+      </c>
+      <c r="C68">
+        <v>-3.146169720624992</v>
+      </c>
+      <c r="D68">
+        <v>4.103030279375009</v>
+      </c>
+      <c r="E68">
+        <v>-0.2548000000000004</v>
+      </c>
+      <c r="F68">
+        <v>7.405200000000001</v>
+      </c>
+      <c r="G68">
+        <v>0.156</v>
+      </c>
+      <c r="H68">
+        <v>3.56</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K68">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L68">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M68">
+        <v>1.76836176</v>
+      </c>
+      <c r="N68">
+        <v>-1.222695093333334</v>
+      </c>
+      <c r="O68">
+        <v>-0.2689929205333334</v>
+      </c>
+      <c r="P68">
+        <v>-0.9537021728000001</v>
+      </c>
+      <c r="Q68">
+        <v>-0.9227021728000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2197796232621065</v>
+      </c>
+      <c r="T68">
+        <v>2.450752831025529</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.06788580786018956</v>
+      </c>
+      <c r="W68">
+        <v>0.2225888690829867</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3085718539099526</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2236337255038875</v>
+      </c>
+      <c r="C69">
+        <v>-3.302766707897629</v>
+      </c>
+      <c r="D69">
+        <v>4.058633292102372</v>
+      </c>
+      <c r="E69">
+        <v>-0.1425999999999998</v>
+      </c>
+      <c r="F69">
+        <v>7.517400000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.156</v>
+      </c>
+      <c r="H69">
+        <v>3.56</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K69">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L69">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M69">
+        <v>1.79515512</v>
+      </c>
+      <c r="N69">
+        <v>-1.249488453333334</v>
+      </c>
+      <c r="O69">
+        <v>-0.2748874597333334</v>
+      </c>
+      <c r="P69">
+        <v>-0.9746009936000003</v>
+      </c>
+      <c r="Q69">
+        <v>-0.9436009936000003</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2252638542700491</v>
+      </c>
+      <c r="T69">
+        <v>2.525018068329333</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06687258684735091</v>
+      </c>
+      <c r="W69">
+        <v>0.2228308262608526</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3039663038515951</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2256337255038875</v>
+      </c>
+      <c r="C70">
+        <v>-3.458413181826854</v>
+      </c>
+      <c r="D70">
+        <v>4.015186818173147</v>
+      </c>
+      <c r="E70">
+        <v>-0.0304000000000002</v>
+      </c>
+      <c r="F70">
+        <v>7.629600000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.156</v>
+      </c>
+      <c r="H70">
+        <v>3.56</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K70">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L70">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M70">
+        <v>1.82194848</v>
+      </c>
+      <c r="N70">
+        <v>-1.276281813333334</v>
+      </c>
+      <c r="O70">
+        <v>-0.2807819989333334</v>
+      </c>
+      <c r="P70">
+        <v>-0.9954998144000002</v>
+      </c>
+      <c r="Q70">
+        <v>-0.9644998144000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2310908497159882</v>
+      </c>
+      <c r="T70">
+        <v>2.603924882964625</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06588916645253694</v>
+      </c>
+      <c r="W70">
+        <v>0.2230656670511342</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2994962111478952</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2276337255038875</v>
+      </c>
+      <c r="C71">
+        <v>-3.613139344009578</v>
+      </c>
+      <c r="D71">
+        <v>3.972660655990423</v>
+      </c>
+      <c r="E71">
+        <v>0.08180000000000032</v>
+      </c>
+      <c r="F71">
+        <v>7.741800000000001</v>
+      </c>
+      <c r="G71">
+        <v>0.156</v>
+      </c>
+      <c r="H71">
+        <v>3.56</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K71">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L71">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M71">
+        <v>1.84874184</v>
+      </c>
+      <c r="N71">
+        <v>-1.303075173333334</v>
+      </c>
+      <c r="O71">
+        <v>-0.2866765381333334</v>
+      </c>
+      <c r="P71">
+        <v>-1.0163986352</v>
+      </c>
+      <c r="Q71">
+        <v>-0.9853986352000004</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2372937803519878</v>
+      </c>
+      <c r="T71">
+        <v>2.687922459834451</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06493425099670307</v>
+      </c>
+      <c r="W71">
+        <v>0.2232937008619873</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2951556863486503</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2296337255038874</v>
+      </c>
+      <c r="C72">
+        <v>-3.766974129952165</v>
+      </c>
+      <c r="D72">
+        <v>3.931025870047836</v>
+      </c>
+      <c r="E72">
+        <v>0.194</v>
+      </c>
+      <c r="F72">
+        <v>7.854000000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.156</v>
+      </c>
+      <c r="H72">
+        <v>3.56</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K72">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L72">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M72">
+        <v>1.8755352</v>
+      </c>
+      <c r="N72">
+        <v>-1.329868533333334</v>
+      </c>
+      <c r="O72">
+        <v>-0.2925710773333334</v>
+      </c>
+      <c r="P72">
+        <v>-1.037297456</v>
+      </c>
+      <c r="Q72">
+        <v>-1.006297456</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.243910239697054</v>
+      </c>
+      <c r="T72">
+        <v>2.777519875162266</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0640066188396073</v>
+      </c>
+      <c r="W72">
+        <v>0.2235152194211018</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2909391765436696</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2316337255038874</v>
+      </c>
+      <c r="C73">
+        <v>-3.919945274727548</v>
+      </c>
+      <c r="D73">
+        <v>3.890254725272452</v>
+      </c>
+      <c r="E73">
+        <v>0.3061999999999987</v>
+      </c>
+      <c r="F73">
+        <v>7.9662</v>
+      </c>
+      <c r="G73">
+        <v>0.156</v>
+      </c>
+      <c r="H73">
+        <v>3.56</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K73">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L73">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M73">
+        <v>1.90232856</v>
+      </c>
+      <c r="N73">
+        <v>-1.356661893333333</v>
+      </c>
+      <c r="O73">
+        <v>-0.2984656165333333</v>
+      </c>
+      <c r="P73">
+        <v>-1.0581962768</v>
+      </c>
+      <c r="Q73">
+        <v>-1.0271962768</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2509830065831593</v>
+      </c>
+      <c r="T73">
+        <v>2.873296422581654</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06310511716581003</v>
+      </c>
+      <c r="W73">
+        <v>0.2237304980208046</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2868414416627729</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2336337255038874</v>
+      </c>
+      <c r="C74">
+        <v>-4.072079374588457</v>
+      </c>
+      <c r="D74">
+        <v>3.850320625411544</v>
+      </c>
+      <c r="E74">
+        <v>0.4183999999999992</v>
+      </c>
+      <c r="F74">
+        <v>8.0784</v>
+      </c>
+      <c r="G74">
+        <v>0.156</v>
+      </c>
+      <c r="H74">
+        <v>3.56</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K74">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L74">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M74">
+        <v>1.92912192</v>
+      </c>
+      <c r="N74">
+        <v>-1.383455253333334</v>
+      </c>
+      <c r="O74">
+        <v>-0.3043601557333334</v>
+      </c>
+      <c r="P74">
+        <v>-1.0790950976</v>
+      </c>
+      <c r="Q74">
+        <v>-1.0480950976</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2585609711039865</v>
+      </c>
+      <c r="T74">
+        <v>2.975914151959571</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06222865720517378</v>
+      </c>
+      <c r="W74">
+        <v>0.2239397966594045</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2828575327507898</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2356337255038875</v>
+      </c>
+      <c r="C75">
+        <v>-4.223401944824373</v>
+      </c>
+      <c r="D75">
+        <v>3.811198055175626</v>
+      </c>
+      <c r="E75">
+        <v>0.5305999999999989</v>
+      </c>
+      <c r="F75">
+        <v>8.1906</v>
+      </c>
+      <c r="G75">
+        <v>0.156</v>
+      </c>
+      <c r="H75">
+        <v>3.56</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K75">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L75">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M75">
+        <v>1.95591528</v>
+      </c>
+      <c r="N75">
+        <v>-1.410248613333333</v>
+      </c>
+      <c r="O75">
+        <v>-0.3102546949333334</v>
+      </c>
+      <c r="P75">
+        <v>-1.0999939184</v>
+      </c>
+      <c r="Q75">
+        <v>-1.0689939184</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.26670026633006</v>
+      </c>
+      <c r="T75">
+        <v>3.08613319462474</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06137620984619879</v>
+      </c>
+      <c r="W75">
+        <v>0.2241433610887278</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2789827720281763</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2376337255038875</v>
+      </c>
+      <c r="C76">
+        <v>-4.373937474126731</v>
+      </c>
+      <c r="D76">
+        <v>3.772862525873268</v>
+      </c>
+      <c r="E76">
+        <v>0.6427999999999985</v>
+      </c>
+      <c r="F76">
+        <v>8.3028</v>
+      </c>
+      <c r="G76">
+        <v>0.156</v>
+      </c>
+      <c r="H76">
+        <v>3.56</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K76">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L76">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M76">
+        <v>1.98270864</v>
+      </c>
+      <c r="N76">
+        <v>-1.437041973333333</v>
+      </c>
+      <c r="O76">
+        <v>-0.3161492341333333</v>
+      </c>
+      <c r="P76">
+        <v>-1.1208927392</v>
+      </c>
+      <c r="Q76">
+        <v>-1.0898927392</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2754656611889085</v>
+      </c>
+      <c r="T76">
+        <v>3.20483062518723</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06054680160503394</v>
+      </c>
+      <c r="W76">
+        <v>0.2243414237767179</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2752127345683362</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2396337255038875</v>
+      </c>
+      <c r="C77">
+        <v>-4.523709475705722</v>
+      </c>
+      <c r="D77">
+        <v>3.735290524294278</v>
+      </c>
+      <c r="E77">
+        <v>0.7549999999999999</v>
+      </c>
+      <c r="F77">
+        <v>8.415000000000001</v>
+      </c>
+      <c r="G77">
+        <v>0.156</v>
+      </c>
+      <c r="H77">
+        <v>3.56</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K77">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L77">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M77">
+        <v>2.009502</v>
+      </c>
+      <c r="N77">
+        <v>-1.463835333333334</v>
+      </c>
+      <c r="O77">
+        <v>-0.3220437733333334</v>
+      </c>
+      <c r="P77">
+        <v>-1.14179156</v>
+      </c>
+      <c r="Q77">
+        <v>-1.11079156</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2849322876364648</v>
+      </c>
+      <c r="T77">
+        <v>3.333023850194719</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05973951091696682</v>
+      </c>
+      <c r="W77">
+        <v>0.2245342047930283</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2715432314407583</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2416337255038875</v>
+      </c>
+      <c r="C78">
+        <v>-4.672740535382952</v>
+      </c>
+      <c r="D78">
+        <v>3.698459464617048</v>
+      </c>
+      <c r="E78">
+        <v>0.8671999999999995</v>
+      </c>
+      <c r="F78">
+        <v>8.527200000000001</v>
+      </c>
+      <c r="G78">
+        <v>0.156</v>
+      </c>
+      <c r="H78">
+        <v>3.56</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K78">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L78">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M78">
+        <v>2.03629536</v>
+      </c>
+      <c r="N78">
+        <v>-1.490628693333334</v>
+      </c>
+      <c r="O78">
+        <v>-0.3279383125333334</v>
+      </c>
+      <c r="P78">
+        <v>-1.1626903808</v>
+      </c>
+      <c r="Q78">
+        <v>-1.1316903808</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2951877996213175</v>
+      </c>
+      <c r="T78">
+        <v>3.471899843952833</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05895346472069094</v>
+      </c>
+      <c r="W78">
+        <v>0.224721912624699</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2679702941849588</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2436337255038875</v>
+      </c>
+      <c r="C79">
+        <v>-4.821052356866634</v>
+      </c>
+      <c r="D79">
+        <v>3.662347643133366</v>
+      </c>
+      <c r="E79">
+        <v>0.9793999999999992</v>
+      </c>
+      <c r="F79">
+        <v>8.6394</v>
+      </c>
+      <c r="G79">
+        <v>0.156</v>
+      </c>
+      <c r="H79">
+        <v>3.56</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K79">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L79">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M79">
+        <v>2.06308872</v>
+      </c>
+      <c r="N79">
+        <v>-1.517422053333333</v>
+      </c>
+      <c r="O79">
+        <v>-0.3338328517333333</v>
+      </c>
+      <c r="P79">
+        <v>-1.1835892016</v>
+      </c>
+      <c r="Q79">
+        <v>-1.1525892016</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.306335095257027</v>
+      </c>
+      <c r="T79">
+        <v>3.622852011081217</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05818783530873393</v>
+      </c>
+      <c r="W79">
+        <v>0.2249047449282743</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2644901604942451</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2456337255038875</v>
+      </c>
+      <c r="C80">
+        <v>-4.968665804400023</v>
+      </c>
+      <c r="D80">
+        <v>3.626934195599979</v>
+      </c>
+      <c r="E80">
+        <v>1.091600000000001</v>
+      </c>
+      <c r="F80">
+        <v>8.751600000000002</v>
+      </c>
+      <c r="G80">
+        <v>0.156</v>
+      </c>
+      <c r="H80">
+        <v>3.56</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K80">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L80">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M80">
+        <v>2.089882080000001</v>
+      </c>
+      <c r="N80">
+        <v>-1.544215413333334</v>
+      </c>
+      <c r="O80">
+        <v>-0.3397273909333335</v>
+      </c>
+      <c r="P80">
+        <v>-1.204488022400001</v>
+      </c>
+      <c r="Q80">
+        <v>-1.173488022400001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3184957814050737</v>
+      </c>
+      <c r="T80">
+        <v>3.787527102493999</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0574418374201604</v>
+      </c>
+      <c r="W80">
+        <v>0.2250828892240657</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2610992610007291</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2476337255038875</v>
+      </c>
+      <c r="C81">
+        <v>-5.115600942959166</v>
+      </c>
+      <c r="D81">
+        <v>3.592199057040835</v>
+      </c>
+      <c r="E81">
+        <v>1.2038</v>
+      </c>
+      <c r="F81">
+        <v>8.863800000000001</v>
+      </c>
+      <c r="G81">
+        <v>0.156</v>
+      </c>
+      <c r="H81">
+        <v>3.56</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K81">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L81">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M81">
+        <v>2.11667544</v>
+      </c>
+      <c r="N81">
+        <v>-1.571008773333334</v>
+      </c>
+      <c r="O81">
+        <v>-0.3456219301333334</v>
+      </c>
+      <c r="P81">
+        <v>-1.2253868432</v>
+      </c>
+      <c r="Q81">
+        <v>-1.1943868432</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3318146281386486</v>
+      </c>
+      <c r="T81">
+        <v>3.967885535946094</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05671472555408243</v>
+      </c>
+      <c r="W81">
+        <v>0.2252565235376851</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.257794207064011</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2496337255038875</v>
+      </c>
+      <c r="C82">
+        <v>-5.261877076162765</v>
+      </c>
+      <c r="D82">
+        <v>3.558122923837235</v>
+      </c>
+      <c r="E82">
+        <v>1.316</v>
+      </c>
+      <c r="F82">
+        <v>8.976000000000001</v>
+      </c>
+      <c r="G82">
+        <v>0.156</v>
+      </c>
+      <c r="H82">
+        <v>3.56</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K82">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L82">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M82">
+        <v>2.1434688</v>
+      </c>
+      <c r="N82">
+        <v>-1.597802133333334</v>
+      </c>
+      <c r="O82">
+        <v>-0.3515164693333334</v>
+      </c>
+      <c r="P82">
+        <v>-1.246285664</v>
+      </c>
+      <c r="Q82">
+        <v>-1.215285664</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3464653595455811</v>
+      </c>
+      <c r="T82">
+        <v>4.166279812743399</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0560057914846564</v>
+      </c>
+      <c r="W82">
+        <v>0.2254258169934641</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2545717794757109</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2516337255038875</v>
+      </c>
+      <c r="C83">
+        <v>-5.40751278204456</v>
+      </c>
+      <c r="D83">
+        <v>3.52468721795544</v>
+      </c>
+      <c r="E83">
+        <v>1.428199999999999</v>
+      </c>
+      <c r="F83">
+        <v>9.088200000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.156</v>
+      </c>
+      <c r="H83">
+        <v>3.56</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K83">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L83">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M83">
+        <v>2.17026216</v>
+      </c>
+      <c r="N83">
+        <v>-1.624595493333333</v>
+      </c>
+      <c r="O83">
+        <v>-0.3574110085333334</v>
+      </c>
+      <c r="P83">
+        <v>-1.2671844848</v>
+      </c>
+      <c r="Q83">
+        <v>-1.2361844848</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3626582732058748</v>
+      </c>
+      <c r="T83">
+        <v>4.385557697624631</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05531436196015448</v>
+      </c>
+      <c r="W83">
+        <v>0.2255909303639151</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2514289180007021</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2536337255038875</v>
+      </c>
+      <c r="C84">
+        <v>-5.55252594682759</v>
+      </c>
+      <c r="D84">
+        <v>3.491874053172412</v>
+      </c>
+      <c r="E84">
+        <v>1.540400000000001</v>
+      </c>
+      <c r="F84">
+        <v>9.200400000000002</v>
+      </c>
+      <c r="G84">
+        <v>0.156</v>
+      </c>
+      <c r="H84">
+        <v>3.56</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K84">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L84">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M84">
+        <v>2.197055520000001</v>
+      </c>
+      <c r="N84">
+        <v>-1.651388853333334</v>
+      </c>
+      <c r="O84">
+        <v>-0.3633055477333335</v>
+      </c>
+      <c r="P84">
+        <v>-1.2880833056</v>
+      </c>
+      <c r="Q84">
+        <v>-1.2570833056</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3806503994950901</v>
+      </c>
+      <c r="T84">
+        <v>4.629199791937111</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05463979657039648</v>
+      </c>
+      <c r="W84">
+        <v>0.2257520165789893</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2483627116836203</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2556337255038875</v>
+      </c>
+      <c r="C85">
+        <v>-5.696933796829315</v>
+      </c>
+      <c r="D85">
+        <v>3.459666203170686</v>
+      </c>
+      <c r="E85">
+        <v>1.652600000000001</v>
+      </c>
+      <c r="F85">
+        <v>9.312600000000002</v>
+      </c>
+      <c r="G85">
+        <v>0.156</v>
+      </c>
+      <c r="H85">
+        <v>3.56</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K85">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L85">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M85">
+        <v>2.223848880000001</v>
+      </c>
+      <c r="N85">
+        <v>-1.678182213333334</v>
+      </c>
+      <c r="O85">
+        <v>-0.3692000869333334</v>
+      </c>
+      <c r="P85">
+        <v>-1.308982126400001</v>
+      </c>
+      <c r="Q85">
+        <v>-1.277982126400001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4007592465242131</v>
+      </c>
+      <c r="T85">
+        <v>4.90150566205106</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05398148576834351</v>
+      </c>
+      <c r="W85">
+        <v>0.2259092211985196</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2453703898561068</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2576337255038875</v>
+      </c>
+      <c r="C86">
+        <v>-5.840752928617199</v>
+      </c>
+      <c r="D86">
+        <v>3.4280470713828</v>
+      </c>
+      <c r="E86">
+        <v>1.764799999999998</v>
+      </c>
+      <c r="F86">
+        <v>9.424799999999999</v>
+      </c>
+      <c r="G86">
+        <v>0.156</v>
+      </c>
+      <c r="H86">
+        <v>3.56</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K86">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L86">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M86">
+        <v>2.25064224</v>
+      </c>
+      <c r="N86">
+        <v>-1.704975573333333</v>
+      </c>
+      <c r="O86">
+        <v>-0.3750946261333333</v>
+      </c>
+      <c r="P86">
+        <v>-1.3298809472</v>
+      </c>
+      <c r="Q86">
+        <v>-1.2988809472</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4233816994319763</v>
+      </c>
+      <c r="T86">
+        <v>5.207849765929248</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0533388490330061</v>
+      </c>
+      <c r="W86">
+        <v>0.2260626828509182</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2424493137863913</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2596337255038874</v>
+      </c>
+      <c r="C87">
+        <v>-5.98399933752563</v>
+      </c>
+      <c r="D87">
+        <v>3.397000662474372</v>
+      </c>
+      <c r="E87">
+        <v>1.877</v>
+      </c>
+      <c r="F87">
+        <v>9.537000000000001</v>
+      </c>
+      <c r="G87">
+        <v>0.156</v>
+      </c>
+      <c r="H87">
+        <v>3.56</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K87">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L87">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M87">
+        <v>2.2774356</v>
+      </c>
+      <c r="N87">
+        <v>-1.731768933333334</v>
+      </c>
+      <c r="O87">
+        <v>-0.3809891653333334</v>
+      </c>
+      <c r="P87">
+        <v>-1.350779768</v>
+      </c>
+      <c r="Q87">
+        <v>-1.319779768</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.449020479394108</v>
+      </c>
+      <c r="T87">
+        <v>5.555039750324531</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05271133316202955</v>
+      </c>
+      <c r="W87">
+        <v>0.2262125336409073</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2395969689183162</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2616337255038875</v>
+      </c>
+      <c r="C88">
+        <v>-6.126688444637157</v>
+      </c>
+      <c r="D88">
+        <v>3.366511555362843</v>
+      </c>
+      <c r="E88">
+        <v>1.989199999999999</v>
+      </c>
+      <c r="F88">
+        <v>9.6492</v>
+      </c>
+      <c r="G88">
+        <v>0.156</v>
+      </c>
+      <c r="H88">
+        <v>3.56</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K88">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L88">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M88">
+        <v>2.30422896</v>
+      </c>
+      <c r="N88">
+        <v>-1.758562293333333</v>
+      </c>
+      <c r="O88">
+        <v>-0.3868837045333333</v>
+      </c>
+      <c r="P88">
+        <v>-1.3716785888</v>
+      </c>
+      <c r="Q88">
+        <v>-1.3406785888</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4783219422079729</v>
+      </c>
+      <c r="T88">
+        <v>5.951828303919141</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05209841068340131</v>
+      </c>
+      <c r="W88">
+        <v>0.2263588995288038</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2368109576518241</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2636337255038875</v>
+      </c>
+      <c r="C89">
+        <v>-6.268835122323683</v>
+      </c>
+      <c r="D89">
+        <v>3.336564877676317</v>
+      </c>
+      <c r="E89">
+        <v>2.101399999999999</v>
+      </c>
+      <c r="F89">
+        <v>9.7614</v>
+      </c>
+      <c r="G89">
+        <v>0.156</v>
+      </c>
+      <c r="H89">
+        <v>3.56</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K89">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L89">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M89">
+        <v>2.33102232</v>
+      </c>
+      <c r="N89">
+        <v>-1.785355653333333</v>
+      </c>
+      <c r="O89">
+        <v>-0.3927782437333334</v>
+      </c>
+      <c r="P89">
+        <v>-1.3925774096</v>
+      </c>
+      <c r="Q89">
+        <v>-1.3615774096</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.512131322377817</v>
+      </c>
+      <c r="T89">
+        <v>6.40966125037446</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05149957837669554</v>
+      </c>
+      <c r="W89">
+        <v>0.2265019006836451</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2340889926213434</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2656337255038875</v>
+      </c>
+      <c r="C90">
+        <v>-6.410453718436449</v>
+      </c>
+      <c r="D90">
+        <v>3.307146281563552</v>
+      </c>
+      <c r="E90">
+        <v>2.2136</v>
+      </c>
+      <c r="F90">
+        <v>9.873600000000001</v>
+      </c>
+      <c r="G90">
+        <v>0.156</v>
+      </c>
+      <c r="H90">
+        <v>3.56</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K90">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L90">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M90">
+        <v>2.35781568</v>
+      </c>
+      <c r="N90">
+        <v>-1.812149013333334</v>
+      </c>
+      <c r="O90">
+        <v>-0.3986727829333334</v>
+      </c>
+      <c r="P90">
+        <v>-1.4134762304</v>
+      </c>
+      <c r="Q90">
+        <v>-1.3824762304</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5515755992426352</v>
+      </c>
+      <c r="T90">
+        <v>6.943799687905666</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05091435589514218</v>
+      </c>
+      <c r="W90">
+        <v>0.2266416518122401</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2314288904324645</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2676337255038874</v>
+      </c>
+      <c r="C91">
+        <v>-6.551558079227509</v>
+      </c>
+      <c r="D91">
+        <v>3.278241920772492</v>
+      </c>
+      <c r="E91">
+        <v>2.3258</v>
+      </c>
+      <c r="F91">
+        <v>9.985800000000001</v>
+      </c>
+      <c r="G91">
+        <v>0.156</v>
+      </c>
+      <c r="H91">
+        <v>3.56</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K91">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L91">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M91">
+        <v>2.38460904</v>
+      </c>
+      <c r="N91">
+        <v>-1.838942373333334</v>
+      </c>
+      <c r="O91">
+        <v>-0.4045673221333334</v>
+      </c>
+      <c r="P91">
+        <v>-1.4343750512</v>
+      </c>
+      <c r="Q91">
+        <v>-1.4033750512</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5981915628101473</v>
+      </c>
+      <c r="T91">
+        <v>7.575054204987999</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05034228448059002</v>
+      </c>
+      <c r="W91">
+        <v>0.2267782624660351</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2288285658208637</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2696337255038875</v>
+      </c>
+      <c r="C92">
+        <v>-6.692161571079633</v>
+      </c>
+      <c r="D92">
+        <v>3.249838428920368</v>
+      </c>
+      <c r="E92">
+        <v>2.438</v>
+      </c>
+      <c r="F92">
+        <v>10.098</v>
+      </c>
+      <c r="G92">
+        <v>0.156</v>
+      </c>
+      <c r="H92">
+        <v>3.56</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K92">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L92">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M92">
+        <v>2.411402400000001</v>
+      </c>
+      <c r="N92">
+        <v>-1.865735733333334</v>
+      </c>
+      <c r="O92">
+        <v>-0.4104618613333335</v>
+      </c>
+      <c r="P92">
+        <v>-1.455273872</v>
+      </c>
+      <c r="Q92">
+        <v>-1.424273872</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6541307190911623</v>
+      </c>
+      <c r="T92">
+        <v>8.3325596254868</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04978292576413902</v>
+      </c>
+      <c r="W92">
+        <v>0.2269118373275236</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2262860262006319</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2716337255038874</v>
+      </c>
+      <c r="C93">
+        <v>-6.832277101116247</v>
+      </c>
+      <c r="D93">
+        <v>3.221922898883753</v>
+      </c>
+      <c r="E93">
+        <v>2.550199999999999</v>
+      </c>
+      <c r="F93">
+        <v>10.2102</v>
+      </c>
+      <c r="G93">
+        <v>0.156</v>
+      </c>
+      <c r="H93">
+        <v>3.56</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K93">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L93">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M93">
+        <v>2.43819576</v>
+      </c>
+      <c r="N93">
+        <v>-1.892529093333333</v>
+      </c>
+      <c r="O93">
+        <v>-0.4163564005333333</v>
+      </c>
+      <c r="P93">
+        <v>-1.4761726928</v>
+      </c>
+      <c r="Q93">
+        <v>-1.4451726928</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7225007989901802</v>
+      </c>
+      <c r="T93">
+        <v>9.258399583874223</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04923586064585178</v>
+      </c>
+      <c r="W93">
+        <v>0.2270424764777706</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2237993665720536</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2736337255038875</v>
+      </c>
+      <c r="C94">
+        <v>-6.971917136758238</v>
+      </c>
+      <c r="D94">
+        <v>3.194482863241764</v>
+      </c>
+      <c r="E94">
+        <v>2.662400000000001</v>
+      </c>
+      <c r="F94">
+        <v>10.3224</v>
+      </c>
+      <c r="G94">
+        <v>0.156</v>
+      </c>
+      <c r="H94">
+        <v>3.56</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K94">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L94">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M94">
+        <v>2.464989120000001</v>
+      </c>
+      <c r="N94">
+        <v>-1.919322453333334</v>
+      </c>
+      <c r="O94">
+        <v>-0.4222509397333335</v>
+      </c>
+      <c r="P94">
+        <v>-1.4970715136</v>
+      </c>
+      <c r="Q94">
+        <v>-1.4660715136</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.807963398863953</v>
+      </c>
+      <c r="T94">
+        <v>10.4156995318585</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0487006882475273</v>
+      </c>
+      <c r="W94">
+        <v>0.2271702756464905</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2213667647614878</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2756337255038875</v>
+      </c>
+      <c r="C95">
+        <v>-7.111093724289807</v>
+      </c>
+      <c r="D95">
+        <v>3.167506275710194</v>
+      </c>
+      <c r="E95">
+        <v>2.7746</v>
+      </c>
+      <c r="F95">
+        <v>10.4346</v>
+      </c>
+      <c r="G95">
+        <v>0.156</v>
+      </c>
+      <c r="H95">
+        <v>3.56</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K95">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L95">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M95">
+        <v>2.49178248</v>
+      </c>
+      <c r="N95">
+        <v>-1.946115813333334</v>
+      </c>
+      <c r="O95">
+        <v>-0.4281454789333334</v>
+      </c>
+      <c r="P95">
+        <v>-1.5179703344</v>
+      </c>
+      <c r="Q95">
+        <v>-1.4869703344</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9178438844159464</v>
+      </c>
+      <c r="T95">
+        <v>11.90365660783829</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04817702493303776</v>
+      </c>
+      <c r="W95">
+        <v>0.2272953264459906</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2189864769683535</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2776337255038875</v>
+      </c>
+      <c r="C96">
+        <v>-7.249818506491545</v>
+      </c>
+      <c r="D96">
+        <v>3.140981493508455</v>
+      </c>
+      <c r="E96">
+        <v>2.8868</v>
+      </c>
+      <c r="F96">
+        <v>10.5468</v>
+      </c>
+      <c r="G96">
+        <v>0.156</v>
+      </c>
+      <c r="H96">
+        <v>3.56</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K96">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L96">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M96">
+        <v>2.51857584</v>
+      </c>
+      <c r="N96">
+        <v>-1.972909173333334</v>
+      </c>
+      <c r="O96">
+        <v>-0.4340400181333334</v>
+      </c>
+      <c r="P96">
+        <v>-1.5388691552</v>
+      </c>
+      <c r="Q96">
+        <v>-1.5078691552</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.064351198485271</v>
+      </c>
+      <c r="T96">
+        <v>13.88759937581134</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04766450339119693</v>
+      </c>
+      <c r="W96">
+        <v>0.2274177165901822</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2166568335963497</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2796337255038874</v>
+      </c>
+      <c r="C97">
+        <v>-7.388102739394862</v>
+      </c>
+      <c r="D97">
+        <v>3.114897260605139</v>
+      </c>
+      <c r="E97">
+        <v>2.999</v>
+      </c>
+      <c r="F97">
+        <v>10.659</v>
+      </c>
+      <c r="G97">
+        <v>0.156</v>
+      </c>
+      <c r="H97">
+        <v>3.56</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K97">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L97">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M97">
+        <v>2.5453692</v>
+      </c>
+      <c r="N97">
+        <v>-1.999702533333333</v>
+      </c>
+      <c r="O97">
+        <v>-0.4399345573333334</v>
+      </c>
+      <c r="P97">
+        <v>-1.559767976</v>
+      </c>
+      <c r="Q97">
+        <v>-1.528767976</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.269461438182326</v>
+      </c>
+      <c r="T97">
+        <v>16.66511925097362</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04716277177655276</v>
+      </c>
+      <c r="W97">
+        <v>0.2275375300997592</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2143762353479671</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2816337255038874</v>
+      </c>
+      <c r="C98">
+        <v>-7.525957308208493</v>
+      </c>
+      <c r="D98">
+        <v>3.089242691791507</v>
+      </c>
+      <c r="E98">
+        <v>3.111199999999999</v>
+      </c>
+      <c r="F98">
+        <v>10.7712</v>
+      </c>
+      <c r="G98">
+        <v>0.156</v>
+      </c>
+      <c r="H98">
+        <v>3.56</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K98">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L98">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M98">
+        <v>2.57216256</v>
+      </c>
+      <c r="N98">
+        <v>-2.026495893333333</v>
+      </c>
+      <c r="O98">
+        <v>-0.4458290965333333</v>
+      </c>
+      <c r="P98">
+        <v>-1.5806667968</v>
+      </c>
+      <c r="Q98">
+        <v>-1.5496667968</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.577126797727904</v>
+      </c>
+      <c r="T98">
+        <v>20.83139906371698</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04667149290388033</v>
+      </c>
+      <c r="W98">
+        <v>0.2276548474945534</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2121431495630925</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2836337255038874</v>
+      </c>
+      <c r="C99">
+        <v>-7.663392742464405</v>
+      </c>
+      <c r="D99">
+        <v>3.064007257535596</v>
+      </c>
+      <c r="E99">
+        <v>3.223399999999999</v>
+      </c>
+      <c r="F99">
+        <v>10.8834</v>
+      </c>
+      <c r="G99">
+        <v>0.156</v>
+      </c>
+      <c r="H99">
+        <v>3.56</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K99">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L99">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M99">
+        <v>2.59895592</v>
+      </c>
+      <c r="N99">
+        <v>-2.053289253333333</v>
+      </c>
+      <c r="O99">
+        <v>-0.4517236357333334</v>
+      </c>
+      <c r="P99">
+        <v>-1.6015656176</v>
+      </c>
+      <c r="Q99">
+        <v>-1.5705656176</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.089902396970539</v>
+      </c>
+      <c r="T99">
+        <v>27.77519875162264</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04619034349250012</v>
+      </c>
+      <c r="W99">
+        <v>0.227769745973991</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2099561067840916</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2856337255038874</v>
+      </c>
+      <c r="C100">
+        <v>-7.800419230427348</v>
+      </c>
+      <c r="D100">
+        <v>3.039180769572651</v>
+      </c>
+      <c r="E100">
+        <v>3.335599999999999</v>
+      </c>
+      <c r="F100">
+        <v>10.9956</v>
+      </c>
+      <c r="G100">
+        <v>0.156</v>
+      </c>
+      <c r="H100">
+        <v>3.56</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K100">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L100">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M100">
+        <v>2.62574928</v>
+      </c>
+      <c r="N100">
+        <v>-2.080082613333333</v>
+      </c>
+      <c r="O100">
+        <v>-0.4576181749333333</v>
+      </c>
+      <c r="P100">
+        <v>-1.6224644384</v>
+      </c>
+      <c r="Q100">
+        <v>-1.5914644384</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.115453595455808</v>
+      </c>
+      <c r="T100">
+        <v>41.66279812743395</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04571901345686238</v>
+      </c>
+      <c r="W100">
+        <v>0.2278822995865013</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2078136975311925</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2876337255038875</v>
+      </c>
+      <c r="C101">
+        <v>-7.937046632809551</v>
+      </c>
+      <c r="D101">
+        <v>3.014753367190449</v>
+      </c>
+      <c r="E101">
+        <v>3.4478</v>
+      </c>
+      <c r="F101">
+        <v>11.1078</v>
+      </c>
+      <c r="G101">
+        <v>0.156</v>
+      </c>
+      <c r="H101">
+        <v>3.56</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="K101">
+        <v>0.03099999999999997</v>
+      </c>
+      <c r="L101">
+        <v>0.5456666666666667</v>
+      </c>
+      <c r="M101">
+        <v>2.652542640000001</v>
+      </c>
+      <c r="N101">
+        <v>-2.106875973333334</v>
+      </c>
+      <c r="O101">
+        <v>-0.4635127141333334</v>
+      </c>
+      <c r="P101">
+        <v>-1.6433632592</v>
+      </c>
+      <c r="Q101">
+        <v>-1.6123632592</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.192107190911615</v>
+      </c>
+      <c r="T101">
+        <v>83.3255962548679</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04525720524012638</v>
+      </c>
+      <c r="W101">
+        <v>0.2279925793886579</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2057145692733018</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
